--- a/业务数据统计模板.xlsx
+++ b/业务数据统计模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenchen\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WasuProject\GitHub\DataStatistic\DataStatistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B429635C-3E01-44DD-A701-1396958D66F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3C8E6A-BA0F-4F7A-B597-9430E855841A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="142">
   <si>
     <t>业务模块</t>
   </si>
@@ -503,6 +503,21 @@
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
+  <si>
+    <t>健康场景用户数</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络场景用户数</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在使用的云存储数</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>云相册付费用户</t>
+  </si>
 </sst>
 </file>
 
@@ -512,7 +527,7 @@
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="177" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -668,6 +683,20 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF2C3E50"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -892,7 +921,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1061,6 +1090,20 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1143,19 +1186,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1433,7 +1463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13.77734375" customWidth="1"/>
@@ -1465,7 +1495,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.2">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="64" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="37" t="s">
@@ -1480,13 +1510,13 @@
         <v>59014</v>
       </c>
       <c r="E2" s="6">
-        <f t="shared" ref="E2:E35" si="0">(C2-D2)/D2</f>
+        <f t="shared" ref="E2:E39" si="0">(C2-D2)/D2</f>
         <v>6.1138035042532284E-2</v>
       </c>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="16.2">
-      <c r="A3" s="59"/>
+      <c r="A3" s="65"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1500,10 +1530,10 @@
         <f t="shared" si="0"/>
         <v>6.1131208447399298E-2</v>
       </c>
-      <c r="F3" s="88"/>
+      <c r="F3" s="59"/>
     </row>
     <row r="4" spans="1:6" ht="16.2">
-      <c r="A4" s="59"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1515,12 +1545,12 @@
       </c>
       <c r="E4" s="6">
         <f t="shared" si="0"/>
-        <v>2.09589168135027E-2</v>
-      </c>
-      <c r="F4" s="89"/>
+        <v>2.0958916813502735E-2</v>
+      </c>
+      <c r="F4" s="60"/>
     </row>
     <row r="5" spans="1:6" ht="16.2">
-      <c r="A5" s="59"/>
+      <c r="A5" s="65"/>
       <c r="B5" s="37" t="s">
         <v>10</v>
       </c>
@@ -1536,10 +1566,10 @@
         <f t="shared" ref="E5:E6" si="1">(C5-D5)/D5</f>
         <v>0.28774686770014868</v>
       </c>
-      <c r="F5" s="90"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="16.2">
-      <c r="A6" s="59"/>
+      <c r="A6" s="65"/>
       <c r="B6" s="37" t="s">
         <v>11</v>
       </c>
@@ -1554,10 +1584,10 @@
         <f t="shared" si="1"/>
         <v>8.3948698017877965E-2</v>
       </c>
-      <c r="F6" s="90"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" ht="16.2">
-      <c r="A7" s="60"/>
+      <c r="A7" s="65"/>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1568,909 +1598,978 @@
         <v>7810</v>
       </c>
       <c r="E7" s="6">
-        <f t="shared" si="0"/>
-        <v>3.1113956466069102E-2</v>
-      </c>
-      <c r="F7" s="90"/>
-    </row>
-    <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="61" t="s">
+        <f>(C7-D7)/D7</f>
+        <v>3.1113956466069143E-2</v>
+      </c>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" ht="16.2">
+      <c r="A8" s="65"/>
+      <c r="B8" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="4">
+        <v>5682</v>
+      </c>
+      <c r="D8" s="5">
+        <v>5612</v>
+      </c>
+      <c r="E8" s="6">
+        <f>(C8-D8)/D8</f>
+        <v>1.2473271560940842E-2</v>
+      </c>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" ht="16.2">
+      <c r="A9" s="66"/>
+      <c r="B9" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="4">
+        <v>5682</v>
+      </c>
+      <c r="D9" s="5">
+        <v>5612</v>
+      </c>
+      <c r="E9" s="6">
+        <f>(C9-D9)/D9</f>
+        <v>1.2473271560940842E-2</v>
+      </c>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" ht="15">
+      <c r="A10" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B10" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C10" s="39">
         <f>统计时间段内的活跃用户!B1</f>
         <v>8405</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D10" s="8">
         <v>8497</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E10" s="9">
         <f t="shared" si="0"/>
         <v>-1.0827350829704601E-2</v>
       </c>
-      <c r="F8" s="91"/>
-    </row>
-    <row r="9" spans="1:6" ht="15">
-      <c r="A9" s="61"/>
-      <c r="B9" s="39" t="s">
+      <c r="F10" s="58"/>
+    </row>
+    <row r="11" spans="1:6" ht="15">
+      <c r="A11" s="67"/>
+      <c r="B11" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C11" s="46">
         <f>统计时间段内的活跃用户!B8</f>
         <v>8516</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D11" s="5">
         <v>8586</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E11" s="9">
         <f t="shared" si="0"/>
         <v>-8.1528068949452605E-3</v>
       </c>
-      <c r="F9" s="91"/>
-    </row>
-    <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="61"/>
-      <c r="B10" s="48" t="s">
+      <c r="F11" s="58"/>
+    </row>
+    <row r="12" spans="1:6" ht="15">
+      <c r="A12" s="67"/>
+      <c r="B12" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C12" s="49">
         <f>统计时间段内的活跃用户!A12</f>
         <v>27729</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D12" s="10">
         <v>23912</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E12" s="11">
         <f t="shared" si="0"/>
         <v>0.1596269655403145</v>
       </c>
-      <c r="F10" s="91"/>
-    </row>
-    <row r="11" spans="1:6" ht="30">
-      <c r="A11" s="60"/>
-      <c r="B11" s="48" t="s">
+      <c r="F12" s="58"/>
+    </row>
+    <row r="13" spans="1:6" ht="30">
+      <c r="A13" s="66"/>
+      <c r="B13" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="49">
+      <c r="C13" s="49">
         <f>统计时间段内的活跃用户!B12</f>
         <v>662245</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D13" s="10">
         <v>656935</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E13" s="11">
         <f t="shared" si="0"/>
         <v>8.0829914679534497E-3</v>
       </c>
-      <c r="F11" s="91"/>
-    </row>
-    <row r="12" spans="1:6" ht="15">
-      <c r="A12" s="62" t="s">
+      <c r="F13" s="58"/>
+    </row>
+    <row r="14" spans="1:6" ht="15">
+      <c r="A14" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B14" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="39">
-        <f>C13+C14+304</f>
+      <c r="C14" s="39">
+        <f>C15+C16+304</f>
         <v>49884</v>
       </c>
-      <c r="D12" s="8">
-        <f>D13+D14+304</f>
+      <c r="D14" s="8">
+        <f>D15+D16+304</f>
         <v>48127</v>
-      </c>
-      <c r="E12" s="9">
-        <f t="shared" si="0"/>
-        <v>3.6507573711222402E-2</v>
-      </c>
-      <c r="F12" s="91"/>
-    </row>
-    <row r="13" spans="1:6" ht="15">
-      <c r="A13" s="62"/>
-      <c r="B13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="8">
-        <v>40159</v>
-      </c>
-      <c r="D13" s="8">
-        <v>38694</v>
-      </c>
-      <c r="E13" s="9">
-        <f t="shared" si="0"/>
-        <v>3.7861167106011298E-2</v>
-      </c>
-      <c r="F13" s="91"/>
-    </row>
-    <row r="14" spans="1:6" ht="15">
-      <c r="A14" s="62"/>
-      <c r="B14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="8">
-        <v>9421</v>
-      </c>
-      <c r="D14" s="8">
-        <v>9129</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="0"/>
-        <v>3.1985978749041501E-2</v>
-      </c>
-      <c r="F14" s="91"/>
+        <v>3.6507573711222388E-2</v>
+      </c>
+      <c r="F14" s="58"/>
     </row>
     <row r="15" spans="1:6" ht="15">
-      <c r="A15" s="62"/>
+      <c r="A15" s="68"/>
       <c r="B15" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="8">
-        <v>23504</v>
+        <v>40159</v>
       </c>
       <c r="D15" s="8">
-        <v>22783</v>
+        <v>38694</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="0"/>
-        <v>3.1646403019795502E-2</v>
-      </c>
-      <c r="F15" s="91"/>
+        <v>3.786116710601127E-2</v>
+      </c>
+      <c r="F15" s="58"/>
     </row>
     <row r="16" spans="1:6" ht="15">
-      <c r="A16" s="62"/>
-      <c r="B16" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="40">
-        <f>C15/(C14+C13)</f>
-        <v>0.47406212182331597</v>
-      </c>
-      <c r="D16" s="12">
-        <f>D15/(D14+D13)</f>
-        <v>0.47640256780210399</v>
+      <c r="A16" s="68"/>
+      <c r="B16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="8">
+        <v>9421</v>
+      </c>
+      <c r="D16" s="8">
+        <v>9129</v>
       </c>
       <c r="E16" s="9">
         <f t="shared" si="0"/>
-        <v>-4.9127484547059697E-3</v>
-      </c>
-      <c r="F16" s="91"/>
+        <v>3.1985978749041515E-2</v>
+      </c>
+      <c r="F16" s="58"/>
     </row>
     <row r="17" spans="1:6" ht="15">
-      <c r="A17" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="39">
-        <f>C18+C19</f>
-        <v>11693</v>
+      <c r="A17" s="68"/>
+      <c r="B17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="8">
+        <v>23504</v>
       </c>
       <c r="D17" s="8">
-        <f>D18+D19</f>
-        <v>11158</v>
+        <v>22783</v>
       </c>
       <c r="E17" s="9">
         <f t="shared" si="0"/>
-        <v>4.7947660871123898E-2</v>
-      </c>
-      <c r="F17" s="91"/>
+        <v>3.164640301979546E-2</v>
+      </c>
+      <c r="F17" s="58"/>
     </row>
     <row r="18" spans="1:6" ht="15">
-      <c r="A18" s="62"/>
-      <c r="B18" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1094</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1008</v>
+      <c r="A18" s="68"/>
+      <c r="B18" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="40">
+        <f>C17/(C16+C15)</f>
+        <v>0.47406212182331586</v>
+      </c>
+      <c r="D18" s="12">
+        <f>D17/(D16+D15)</f>
+        <v>0.4764025678021036</v>
       </c>
       <c r="E18" s="9">
         <f t="shared" si="0"/>
-        <v>8.5317460317460306E-2</v>
-      </c>
-      <c r="F18" s="91"/>
+        <v>-4.9127484547059723E-3</v>
+      </c>
+      <c r="F18" s="58"/>
     </row>
     <row r="19" spans="1:6" ht="15">
-      <c r="A19" s="62"/>
-      <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="8">
-        <v>10599</v>
+      <c r="A19" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="39">
+        <f>C20+C21</f>
+        <v>11693</v>
       </c>
       <c r="D19" s="8">
-        <v>10150</v>
+        <f>D20+D21</f>
+        <v>11158</v>
       </c>
       <c r="E19" s="9">
         <f t="shared" si="0"/>
-        <v>4.4236453201970401E-2</v>
-      </c>
-      <c r="F19" s="91"/>
+        <v>4.7947660871123857E-2</v>
+      </c>
+      <c r="F19" s="58"/>
     </row>
     <row r="20" spans="1:6" ht="15">
-      <c r="A20" s="62"/>
+      <c r="A20" s="68"/>
       <c r="B20" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" s="8">
-        <v>45209</v>
+        <v>1094</v>
       </c>
       <c r="D20" s="8">
-        <v>43740</v>
+        <v>1008</v>
       </c>
       <c r="E20" s="9">
         <f t="shared" si="0"/>
-        <v>3.3584819387288502E-2</v>
-      </c>
-      <c r="F20" s="91"/>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1">
-      <c r="A21" s="63" t="s">
+        <v>8.531746031746032E-2</v>
+      </c>
+      <c r="F20" s="58"/>
+    </row>
+    <row r="21" spans="1:6" ht="15">
+      <c r="A21" s="68"/>
+      <c r="B21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="8">
+        <v>10599</v>
+      </c>
+      <c r="D21" s="8">
+        <v>10150</v>
+      </c>
+      <c r="E21" s="9">
+        <f t="shared" si="0"/>
+        <v>4.4236453201970442E-2</v>
+      </c>
+      <c r="F21" s="58"/>
+    </row>
+    <row r="22" spans="1:6" ht="15">
+      <c r="A22" s="68"/>
+      <c r="B22" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="8">
+        <v>45209</v>
+      </c>
+      <c r="D22" s="8">
+        <v>43740</v>
+      </c>
+      <c r="E22" s="9">
+        <f t="shared" si="0"/>
+        <v>3.3584819387288523E-2</v>
+      </c>
+      <c r="F22" s="58"/>
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1">
+      <c r="A23" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B23" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="39">
+      <c r="C23" s="39">
         <f>业务数据统计!D31</f>
         <v>1465</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D23" s="8">
         <v>1461</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E23" s="9">
         <f t="shared" si="0"/>
         <v>2.7378507871321013E-3</v>
       </c>
-      <c r="F21" s="91"/>
-    </row>
-    <row r="22" spans="1:6" ht="15">
-      <c r="A22" s="64"/>
-      <c r="B22" s="39" t="s">
+      <c r="F23" s="58"/>
+    </row>
+    <row r="24" spans="1:6" ht="15">
+      <c r="A24" s="70"/>
+      <c r="B24" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C24" s="39">
         <f>业务数据统计!D32-业务数据统计!G32</f>
         <v>45</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D24" s="8">
         <v>45</v>
-      </c>
-      <c r="E22" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="91"/>
-    </row>
-    <row r="23" spans="1:6" ht="15">
-      <c r="A23" s="64"/>
-      <c r="B23" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="39">
-        <f>业务数据统计!G32</f>
-        <v>6801</v>
-      </c>
-      <c r="D23" s="8">
-        <v>6138</v>
-      </c>
-      <c r="E23" s="9">
-        <f t="shared" si="0"/>
-        <v>0.10801564027370479</v>
-      </c>
-      <c r="F23" s="91"/>
-    </row>
-    <row r="24" spans="1:6" ht="15">
-      <c r="A24" s="64"/>
-      <c r="B24" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="39">
-        <f>业务数据统计!D33</f>
-        <v>190</v>
-      </c>
-      <c r="D24" s="8">
-        <v>190</v>
       </c>
       <c r="E24" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F24" s="91"/>
+      <c r="F24" s="58"/>
     </row>
     <row r="25" spans="1:6" ht="15">
-      <c r="A25" s="64"/>
+      <c r="A25" s="70"/>
       <c r="B25" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="39">
+        <f>业务数据统计!G32</f>
+        <v>6801</v>
+      </c>
+      <c r="D25" s="8">
+        <v>6138</v>
+      </c>
+      <c r="E25" s="9">
+        <f t="shared" si="0"/>
+        <v>0.10801564027370479</v>
+      </c>
+      <c r="F25" s="58"/>
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="A26" s="70"/>
+      <c r="B26" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="39">
+        <f>业务数据统计!D33</f>
+        <v>190</v>
+      </c>
+      <c r="D26" s="8">
+        <v>190</v>
+      </c>
+      <c r="E26" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="58"/>
+    </row>
+    <row r="27" spans="1:6" ht="15">
+      <c r="A27" s="70"/>
+      <c r="B27" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="39">
+      <c r="C27" s="39">
         <f>业务数据统计!D34-业务数据统计!G34</f>
         <v>5</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D27" s="8">
         <v>5</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E27" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F25" s="91"/>
-    </row>
-    <row r="26" spans="1:6" ht="15">
-      <c r="A26" s="65"/>
-      <c r="B26" s="39" t="s">
+      <c r="F27" s="58"/>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" s="71"/>
+      <c r="B28" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="39">
+      <c r="C28" s="39">
         <f>业务数据统计!G34</f>
         <v>283</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D28" s="8">
         <v>281</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E28" s="9">
         <f t="shared" si="0"/>
         <v>7.1174377224199285E-3</v>
       </c>
-      <c r="F26" s="91"/>
-    </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1">
-      <c r="A27" s="62" t="s">
+      <c r="F28" s="58"/>
+    </row>
+    <row r="29" spans="1:6" ht="15" customHeight="1">
+      <c r="A29" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B29" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="39">
-        <f>5859+C18</f>
+      <c r="C29" s="39">
+        <f>5859+C20</f>
         <v>6953</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D29" s="8">
         <f>5521+994</f>
         <v>6515</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E29" s="9">
         <f t="shared" si="0"/>
-        <v>6.7229470452801199E-2</v>
-      </c>
-      <c r="F27" s="91"/>
-    </row>
-    <row r="28" spans="1:6" ht="15">
-      <c r="A28" s="66"/>
-      <c r="B28" s="8" t="s">
+        <v>6.7229470452801227E-2</v>
+      </c>
+      <c r="F29" s="58"/>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" s="72"/>
+      <c r="B30" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C30" s="12">
         <v>0.46300000000000002</v>
       </c>
-      <c r="D28" s="12">
-        <f>D27/14514</f>
-        <v>0.44887694639658299</v>
-      </c>
-      <c r="E28" s="13">
+      <c r="D30" s="12">
+        <f>D29/14514</f>
+        <v>0.4488769463965826</v>
+      </c>
+      <c r="E30" s="13">
         <f t="shared" si="0"/>
-        <v>3.1463085188026811E-2</v>
-      </c>
-      <c r="F28" s="91"/>
-    </row>
-    <row r="29" spans="1:6" ht="15">
-      <c r="A29" s="66"/>
-      <c r="B29" s="39" t="s">
+        <v>3.1463085188027706E-2</v>
+      </c>
+      <c r="F30" s="58"/>
+    </row>
+    <row r="31" spans="1:6" ht="15">
+      <c r="A31" s="72"/>
+      <c r="B31" s="61" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="8">
+        <v>1963</v>
+      </c>
+      <c r="D31" s="8">
+        <v>2114</v>
+      </c>
+      <c r="E31" s="9">
+        <f t="shared" si="0"/>
+        <v>-7.1428571428571425E-2</v>
+      </c>
+      <c r="F31" s="58"/>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" s="72"/>
+      <c r="B32" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="39">
+      <c r="C32" s="39">
         <f>业务数据统计!D21</f>
         <v>3615</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D32" s="8">
         <v>3400</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E32" s="9">
         <f t="shared" si="0"/>
         <v>6.3235294117647056E-2</v>
       </c>
-      <c r="F29" s="91"/>
-    </row>
-    <row r="30" spans="1:6" ht="15">
-      <c r="A30" s="66"/>
-      <c r="B30" s="39" t="s">
+      <c r="F32" s="58"/>
+    </row>
+    <row r="33" spans="1:7" ht="15">
+      <c r="A33" s="72"/>
+      <c r="B33" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="40">
-        <f>C17/C15</f>
+      <c r="C33" s="40">
+        <f>C19/C17</f>
         <v>0.49748978897208984</v>
       </c>
-      <c r="D30" s="12">
-        <f>D17/D15</f>
-        <v>0.489751130228679</v>
-      </c>
-      <c r="E30" s="9">
+      <c r="D33" s="12">
+        <f>D19/D17</f>
+        <v>0.48975113022867928</v>
+      </c>
+      <c r="E33" s="9">
         <f t="shared" si="0"/>
-        <v>1.5801206502162515E-2</v>
-      </c>
-      <c r="F30" s="91"/>
-    </row>
-    <row r="31" spans="1:6" ht="15">
-      <c r="A31" s="66"/>
-      <c r="B31" s="39" t="s">
+        <v>1.5801206502161939E-2</v>
+      </c>
+      <c r="F33" s="58"/>
+    </row>
+    <row r="34" spans="1:7" ht="15">
+      <c r="A34" s="72"/>
+      <c r="B34" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="40">
-        <f>业务数据统计!D20/主表!C17</f>
+      <c r="C34" s="40">
+        <f>业务数据统计!D20/主表!C19</f>
         <v>0.75395535790643975</v>
       </c>
-      <c r="D31" s="12">
-        <f>8215/D17</f>
-        <v>0.73624305431080805</v>
-      </c>
-      <c r="E31" s="13">
+      <c r="D34" s="12">
+        <f>8215/D19</f>
+        <v>0.73624305431080839</v>
+      </c>
+      <c r="E34" s="13">
         <f t="shared" si="0"/>
-        <v>2.4057685151559167E-2</v>
-      </c>
-      <c r="F31" s="91"/>
-    </row>
-    <row r="32" spans="1:6" ht="15">
-      <c r="A32" s="62" t="s">
+        <v>2.4057685151558702E-2</v>
+      </c>
+      <c r="F34" s="58"/>
+    </row>
+    <row r="35" spans="1:7" ht="15">
+      <c r="A35" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B35" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="39">
+      <c r="C35" s="39">
         <f>业务数据统计!D3</f>
         <v>10901</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D35" s="14">
         <v>7295</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E35" s="9">
         <f t="shared" si="0"/>
         <v>0.49431117203564084</v>
       </c>
-      <c r="F32" s="91"/>
-    </row>
-    <row r="33" spans="1:6" ht="15">
-      <c r="A33" s="66"/>
-      <c r="B33" s="39" t="s">
+      <c r="F35" s="58"/>
+    </row>
+    <row r="36" spans="1:7" ht="15">
+      <c r="A36" s="72"/>
+      <c r="B36" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="39">
+      <c r="C36" s="39">
         <f>业务数据统计!D4</f>
         <v>1537</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D36" s="14">
         <v>1458</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E36" s="9">
         <f t="shared" si="0"/>
         <v>5.4183813443072701E-2</v>
       </c>
-      <c r="F33" s="91"/>
-    </row>
-    <row r="34" spans="1:6" ht="15">
-      <c r="A34" s="66"/>
-      <c r="B34" s="39" t="s">
+      <c r="F36" s="58"/>
+    </row>
+    <row r="37" spans="1:7" ht="15">
+      <c r="A37" s="72"/>
+      <c r="B37" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="39">
+      <c r="C37" s="39">
         <f>业务数据统计!D5</f>
         <v>602820</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D37" s="14">
         <v>121740</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E37" s="9">
         <f t="shared" si="0"/>
         <v>3.9517003449975356</v>
       </c>
-      <c r="F34" s="91"/>
-    </row>
-    <row r="35" spans="1:6" ht="15">
-      <c r="A35" s="66"/>
-      <c r="B35" s="39" t="s">
+      <c r="F37" s="58"/>
+    </row>
+    <row r="38" spans="1:7" ht="15">
+      <c r="A38" s="72"/>
+      <c r="B38" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C38" s="39">
         <f>业务数据统计!D6</f>
         <v>1777</v>
       </c>
-      <c r="D35" s="92">
+      <c r="D38" s="14">
         <v>1735</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E38" s="9">
+        <f t="shared" ref="E38" si="2">(C38-D38)/D38</f>
+        <v>2.420749279538905E-2</v>
+      </c>
+      <c r="F38" s="58"/>
+      <c r="G38" s="62"/>
+    </row>
+    <row r="39" spans="1:7" ht="15">
+      <c r="A39" s="72"/>
+      <c r="B39" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="C39" s="39">
+        <v>1856</v>
+      </c>
+      <c r="D39" s="14">
+        <v>1735</v>
+      </c>
+      <c r="E39" s="9">
         <f t="shared" si="0"/>
-        <v>2.420749279538905E-2</v>
-      </c>
-      <c r="F35" s="91"/>
-    </row>
-    <row r="36" spans="1:6" ht="15">
-      <c r="A36" s="62" t="s">
+        <v>6.9740634005763691E-2</v>
+      </c>
+      <c r="F39" s="58"/>
+    </row>
+    <row r="40" spans="1:7" ht="15">
+      <c r="A40" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="39" t="s">
+      <c r="B40" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C40" s="39">
         <f>业务数据统计!D16</f>
         <v>1335</v>
       </c>
-      <c r="D36" s="12">
-        <f>C36/C33</f>
+      <c r="D40" s="12">
+        <f>C40/C36</f>
         <v>0.86857514638906963</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="91"/>
-    </row>
-    <row r="37" spans="1:6" ht="15">
-      <c r="A37" s="66"/>
-      <c r="B37" s="39" t="s">
+      <c r="E40" s="9"/>
+      <c r="F40" s="58"/>
+    </row>
+    <row r="41" spans="1:7" ht="15">
+      <c r="A41" s="72"/>
+      <c r="B41" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="39">
+      <c r="C41" s="39">
         <f>业务数据统计!D18</f>
         <v>325</v>
       </c>
-      <c r="D37" s="12">
-        <f>C37/C33</f>
+      <c r="D41" s="12">
+        <f>C41/C36</f>
         <v>0.2114508783344177</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="91"/>
-    </row>
-    <row r="38" spans="1:6" ht="15">
-      <c r="A38" s="66"/>
-      <c r="B38" s="39" t="s">
+      <c r="E41" s="9"/>
+      <c r="F41" s="58"/>
+    </row>
+    <row r="42" spans="1:7" ht="15">
+      <c r="A42" s="72"/>
+      <c r="B42" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="39">
+      <c r="C42" s="39">
         <f>业务数据统计!D17</f>
         <v>4</v>
       </c>
-      <c r="D38" s="12">
-        <f>C38/C33</f>
+      <c r="D42" s="12">
+        <f>C42/C36</f>
         <v>2.6024723487312949E-3</v>
       </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="91"/>
-    </row>
-    <row r="39" spans="1:6" ht="15">
-      <c r="A39" s="66"/>
-      <c r="B39" s="39" t="s">
+      <c r="E42" s="9"/>
+      <c r="F42" s="58"/>
+    </row>
+    <row r="43" spans="1:7" ht="15">
+      <c r="A43" s="72"/>
+      <c r="B43" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="39">
+      <c r="C43" s="39">
         <f>业务数据统计!D19</f>
         <v>9</v>
       </c>
-      <c r="D39" s="12">
-        <f>C39/C33</f>
+      <c r="D43" s="12">
+        <f>C43/C36</f>
         <v>5.8555627846454128E-3</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="91"/>
-    </row>
-    <row r="40" spans="1:6" ht="15">
-      <c r="A40" s="62" t="s">
+      <c r="E43" s="9"/>
+      <c r="F43" s="58"/>
+    </row>
+    <row r="44" spans="1:7" ht="15">
+      <c r="A44" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="39" t="s">
+      <c r="B44" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="41">
+      <c r="C44" s="41">
         <f>业务数据统计!D35</f>
         <v>321</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D44" s="14">
         <v>321</v>
       </c>
-      <c r="E40" s="9">
-        <f t="shared" ref="E40:E54" si="2">(C40-D40)/D40</f>
+      <c r="E44" s="9">
+        <f t="shared" ref="E44:E58" si="3">(C44-D44)/D44</f>
         <v>0</v>
       </c>
-      <c r="F40" s="91"/>
-    </row>
-    <row r="41" spans="1:6" ht="15">
-      <c r="A41" s="66"/>
-      <c r="B41" s="39" t="s">
+      <c r="F44" s="58"/>
+    </row>
+    <row r="45" spans="1:7" ht="15">
+      <c r="A45" s="72"/>
+      <c r="B45" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="41">
+      <c r="C45" s="41">
         <f>业务数据统计!D36</f>
         <v>87707</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D45" s="14">
         <v>79012</v>
       </c>
-      <c r="E41" s="9">
-        <f t="shared" si="2"/>
+      <c r="E45" s="9">
+        <f t="shared" si="3"/>
         <v>0.11004657520376651</v>
       </c>
-      <c r="F41" s="91"/>
-    </row>
-    <row r="42" spans="1:6" ht="15">
-      <c r="A42" s="66"/>
-      <c r="B42" s="39" t="s">
+      <c r="F45" s="58"/>
+    </row>
+    <row r="46" spans="1:7" ht="15">
+      <c r="A46" s="72"/>
+      <c r="B46" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="41">
+      <c r="C46" s="41">
         <f>业务数据统计!D37</f>
         <v>63519.1</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D46" s="14">
         <v>57685.66</v>
       </c>
-      <c r="E42" s="9">
-        <f t="shared" si="2"/>
+      <c r="E46" s="9">
+        <f t="shared" si="3"/>
         <v>0.10112461225198767</v>
       </c>
-      <c r="F42" s="91"/>
-    </row>
-    <row r="43" spans="1:6" ht="15">
-      <c r="A43" s="66"/>
-      <c r="B43" s="39" t="s">
+      <c r="F46" s="58"/>
+    </row>
+    <row r="47" spans="1:7" ht="15">
+      <c r="A47" s="72"/>
+      <c r="B47" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C43" s="41">
+      <c r="C47" s="41">
         <f>业务数据统计!D38</f>
         <v>36170.99</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D47" s="14">
         <v>32900.660000000003</v>
       </c>
-      <c r="E43" s="9">
-        <f t="shared" si="2"/>
+      <c r="E47" s="9">
+        <f t="shared" si="3"/>
         <v>9.9400133614340691E-2</v>
       </c>
-      <c r="F43" s="91"/>
-    </row>
-    <row r="44" spans="1:6" ht="15">
-      <c r="A44" s="66"/>
-      <c r="B44" s="39" t="s">
+      <c r="F47" s="58"/>
+    </row>
+    <row r="48" spans="1:7" ht="15">
+      <c r="A48" s="72"/>
+      <c r="B48" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="41">
+      <c r="C48" s="41">
         <f>业务数据统计!D39</f>
         <v>27348.11</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D48" s="14">
         <v>24785</v>
       </c>
-      <c r="E44" s="9">
-        <f t="shared" si="2"/>
+      <c r="E48" s="9">
+        <f t="shared" si="3"/>
         <v>0.10341375832156549</v>
       </c>
-      <c r="F44" s="91"/>
-    </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1">
-      <c r="A45" s="63" t="s">
+      <c r="F48" s="58"/>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1">
+      <c r="A49" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B45" s="39" t="s">
+      <c r="B49" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C45" s="52">
+      <c r="C49" s="52">
         <f>'云相册-城市统计'!B2</f>
         <v>315</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D49" s="15">
         <v>301</v>
       </c>
-      <c r="E45" s="9">
-        <f t="shared" si="2"/>
+      <c r="E49" s="9">
+        <f t="shared" si="3"/>
         <v>4.6511627906976744E-2</v>
       </c>
-      <c r="F45" s="53" t="str">
+      <c r="F49" s="53" t="str">
         <f>'云相册-城市统计'!A2</f>
         <v>杭州市</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15.6">
-      <c r="A46" s="64"/>
-      <c r="B46" s="39" t="s">
+    <row r="50" spans="1:6" ht="15.6">
+      <c r="A50" s="70"/>
+      <c r="B50" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C46" s="52">
+      <c r="C50" s="52">
         <f>'云相册-城市统计'!B3</f>
         <v>86</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D50" s="16">
         <v>75</v>
       </c>
-      <c r="E46" s="9">
-        <f t="shared" si="2"/>
+      <c r="E50" s="9">
+        <f t="shared" si="3"/>
         <v>0.14666666666666667</v>
       </c>
-      <c r="F46" s="53" t="str">
+      <c r="F50" s="53" t="str">
         <f>'云相册-城市统计'!A3</f>
         <v>金华市</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15.6">
-      <c r="A47" s="64"/>
-      <c r="B47" s="39" t="s">
+    <row r="51" spans="1:6" ht="15.6">
+      <c r="A51" s="70"/>
+      <c r="B51" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="C47" s="52">
+      <c r="C51" s="52">
         <f>'云相册-城市统计'!B4</f>
         <v>55</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D51" s="16">
         <v>54</v>
       </c>
-      <c r="E47" s="9">
-        <f t="shared" si="2"/>
+      <c r="E51" s="9">
+        <f t="shared" si="3"/>
         <v>1.8518518518518517E-2</v>
       </c>
-      <c r="F47" s="53" t="str">
+      <c r="F51" s="53" t="str">
         <f>'云相册-城市统计'!A4</f>
         <v>绍兴市</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15.6">
-      <c r="A48" s="64"/>
-      <c r="B48" s="39" t="s">
+    <row r="52" spans="1:6" ht="15.6">
+      <c r="A52" s="70"/>
+      <c r="B52" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="52">
+      <c r="C52" s="52">
         <f>'云相册-城市统计'!B5</f>
         <v>49</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D52" s="16">
         <v>46</v>
       </c>
-      <c r="E48" s="9">
-        <f t="shared" si="2"/>
+      <c r="E52" s="9">
+        <f t="shared" si="3"/>
         <v>6.5217391304347824E-2</v>
       </c>
-      <c r="F48" s="53" t="str">
+      <c r="F52" s="53" t="str">
         <f>'云相册-城市统计'!A5</f>
         <v>湖州市</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15.6">
-      <c r="A49" s="64"/>
-      <c r="B49" s="39" t="s">
+    <row r="53" spans="1:6" ht="15.6">
+      <c r="A53" s="70"/>
+      <c r="B53" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="52">
+      <c r="C53" s="52">
         <f>'云相册-城市统计'!B6</f>
         <v>46</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D53" s="16">
         <v>40</v>
       </c>
-      <c r="E49" s="9">
-        <f t="shared" si="2"/>
+      <c r="E53" s="9">
+        <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
-      <c r="F49" s="53" t="str">
+      <c r="F53" s="53" t="str">
         <f>'云相册-城市统计'!A6</f>
         <v>衢州市</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.6">
-      <c r="A50" s="64"/>
-      <c r="B50" s="39" t="s">
+    <row r="54" spans="1:6" ht="15.6">
+      <c r="A54" s="70"/>
+      <c r="B54" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="52">
+      <c r="C54" s="52">
         <f>'云相册-城市统计'!B7</f>
         <v>45</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D54" s="16">
         <v>43</v>
       </c>
-      <c r="E50" s="9">
-        <f t="shared" si="2"/>
+      <c r="E54" s="9">
+        <f t="shared" si="3"/>
         <v>4.6511627906976744E-2</v>
       </c>
-      <c r="F50" s="53" t="str">
+      <c r="F54" s="53" t="str">
         <f>'云相册-城市统计'!A7</f>
         <v>嘉兴市</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15.6">
-      <c r="A51" s="64"/>
-      <c r="B51" s="39" t="s">
+    <row r="55" spans="1:6" ht="15.6">
+      <c r="A55" s="70"/>
+      <c r="B55" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="C51" s="52">
+      <c r="C55" s="52">
         <f>'云相册-城市统计'!B8</f>
         <v>35</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D55" s="16">
         <v>35</v>
       </c>
-      <c r="E51" s="9">
-        <f t="shared" si="2"/>
+      <c r="E55" s="9">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F51" s="53" t="str">
+      <c r="F55" s="53" t="str">
         <f>'云相册-城市统计'!A8</f>
         <v>上海市</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.6">
-      <c r="A52" s="64"/>
-      <c r="B52" s="39" t="s">
+    <row r="56" spans="1:6" ht="15.6">
+      <c r="A56" s="70"/>
+      <c r="B56" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="C52" s="52">
+      <c r="C56" s="52">
         <f>'云相册-城市统计'!B9</f>
         <v>33</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D56" s="16">
         <v>33</v>
       </c>
-      <c r="E52" s="9">
-        <f t="shared" si="2"/>
+      <c r="E56" s="9">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F52" s="53" t="str">
+      <c r="F56" s="53" t="str">
         <f>'云相册-城市统计'!A9</f>
         <v>温州市</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.6">
-      <c r="A53" s="64"/>
-      <c r="B53" s="39" t="s">
+    <row r="57" spans="1:6" ht="15.6">
+      <c r="A57" s="70"/>
+      <c r="B57" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="52">
+      <c r="C57" s="52">
         <f>'云相册-城市统计'!B10</f>
         <v>33</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D57" s="16">
         <v>31</v>
       </c>
-      <c r="E53" s="9">
-        <f t="shared" si="2"/>
+      <c r="E57" s="9">
+        <f t="shared" si="3"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="F53" s="53" t="str">
+      <c r="F57" s="53" t="str">
         <f>'云相册-城市统计'!A10</f>
         <v>六安市</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.6">
-      <c r="A54" s="65"/>
-      <c r="B54" s="39" t="s">
+    <row r="58" spans="1:6" ht="15.6">
+      <c r="A58" s="71"/>
+      <c r="B58" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="C54" s="52">
+      <c r="C58" s="52">
         <f>'云相册-城市统计'!B11</f>
         <v>32</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D58" s="16">
         <v>31</v>
       </c>
-      <c r="E54" s="9">
-        <f t="shared" si="2"/>
+      <c r="E58" s="9">
+        <f t="shared" si="3"/>
         <v>3.2258064516129031E-2</v>
       </c>
-      <c r="F54" s="53" t="str">
+      <c r="F58" s="53" t="str">
         <f>'云相册-城市统计'!A11</f>
         <v>宁波市</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A44"/>
-    <mergeCell ref="A45:A54"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="A29:A34"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A44:A48"/>
+    <mergeCell ref="A49:A58"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A28"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2539,12 +2638,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="69"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="75"/>
       <c r="E1" s="18"/>
       <c r="F1" s="19" t="s">
         <v>80</v>
@@ -2554,10 +2653,10 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="71"/>
+      <c r="B2" s="77"/>
       <c r="C2" s="20" t="s">
         <v>83</v>
       </c>
@@ -2571,10 +2670,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="81" t="s">
         <v>84</v>
       </c>
       <c r="C3" s="22" t="s">
@@ -2588,8 +2687,8 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="73"/>
-      <c r="B4" s="76"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="23" t="s">
         <v>44</v>
       </c>
@@ -2601,8 +2700,8 @@
       <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="73"/>
-      <c r="B5" s="75" t="s">
+      <c r="A5" s="79"/>
+      <c r="B5" s="81" t="s">
         <v>86</v>
       </c>
       <c r="C5" s="23" t="s">
@@ -2616,8 +2715,8 @@
       <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="73"/>
-      <c r="B6" s="76"/>
+      <c r="A6" s="79"/>
+      <c r="B6" s="82"/>
       <c r="C6" s="24" t="s">
         <v>88</v>
       </c>
@@ -2629,8 +2728,8 @@
       <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="73"/>
-      <c r="B7" s="77" t="s">
+      <c r="A7" s="79"/>
+      <c r="B7" s="83" t="s">
         <v>89</v>
       </c>
       <c r="C7" s="25" t="s">
@@ -2644,8 +2743,8 @@
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="73"/>
-      <c r="B8" s="78"/>
+      <c r="A8" s="79"/>
+      <c r="B8" s="84"/>
       <c r="C8" s="25" t="s">
         <v>91</v>
       </c>
@@ -2657,8 +2756,8 @@
       <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="73"/>
-      <c r="B9" s="78"/>
+      <c r="A9" s="79"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="25" t="s">
         <v>92</v>
       </c>
@@ -2670,8 +2769,8 @@
       <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="73"/>
-      <c r="B10" s="79"/>
+      <c r="A10" s="79"/>
+      <c r="B10" s="85"/>
       <c r="C10" s="25" t="s">
         <v>93</v>
       </c>
@@ -2683,8 +2782,8 @@
       <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="73"/>
-      <c r="B11" s="77" t="s">
+      <c r="A11" s="79"/>
+      <c r="B11" s="83" t="s">
         <v>94</v>
       </c>
       <c r="C11" s="25" t="s">
@@ -2698,8 +2797,8 @@
       <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="73"/>
-      <c r="B12" s="78"/>
+      <c r="A12" s="79"/>
+      <c r="B12" s="84"/>
       <c r="C12" s="25" t="s">
         <v>96</v>
       </c>
@@ -2711,8 +2810,8 @@
       <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="73"/>
-      <c r="B13" s="78"/>
+      <c r="A13" s="79"/>
+      <c r="B13" s="84"/>
       <c r="C13" s="25" t="s">
         <v>97</v>
       </c>
@@ -2724,8 +2823,8 @@
       <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="73"/>
-      <c r="B14" s="79"/>
+      <c r="A14" s="79"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="25" t="s">
         <v>98</v>
       </c>
@@ -2737,8 +2836,8 @@
       <c r="G14" s="18"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="73"/>
-      <c r="B15" s="75" t="s">
+      <c r="A15" s="79"/>
+      <c r="B15" s="81" t="s">
         <v>99</v>
       </c>
       <c r="C15" s="23" t="s">
@@ -2752,8 +2851,8 @@
       <c r="G15" s="18"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="73"/>
-      <c r="B16" s="80"/>
+      <c r="A16" s="79"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="23" t="s">
         <v>102</v>
       </c>
@@ -2765,8 +2864,8 @@
       <c r="G16" s="18"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="73"/>
-      <c r="B17" s="80"/>
+      <c r="A17" s="79"/>
+      <c r="B17" s="86"/>
       <c r="C17" s="23" t="s">
         <v>103</v>
       </c>
@@ -2778,8 +2877,8 @@
       <c r="G17" s="18"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="73"/>
-      <c r="B18" s="80"/>
+      <c r="A18" s="79"/>
+      <c r="B18" s="86"/>
       <c r="C18" s="23" t="s">
         <v>104</v>
       </c>
@@ -2791,8 +2890,8 @@
       <c r="G18" s="18"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="74"/>
-      <c r="B19" s="76"/>
+      <c r="A19" s="80"/>
+      <c r="B19" s="82"/>
       <c r="C19" s="28" t="s">
         <v>105</v>
       </c>
@@ -2804,10 +2903,10 @@
       <c r="G19" s="18"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="81" t="s">
         <v>107</v>
       </c>
       <c r="C20" s="20" t="s">
@@ -2821,8 +2920,8 @@
       <c r="G20" s="18"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="82"/>
-      <c r="B21" s="80"/>
+      <c r="A21" s="88"/>
+      <c r="B21" s="86"/>
       <c r="C21" s="20" t="s">
         <v>39</v>
       </c>
@@ -2834,8 +2933,8 @@
       <c r="G21" s="18"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="82"/>
-      <c r="B22" s="80"/>
+      <c r="A22" s="88"/>
+      <c r="B22" s="86"/>
       <c r="C22" s="23" t="s">
         <v>109</v>
       </c>
@@ -2847,8 +2946,8 @@
       <c r="G22" s="18"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="82"/>
-      <c r="B23" s="80"/>
+      <c r="A23" s="88"/>
+      <c r="B23" s="86"/>
       <c r="C23" s="23" t="s">
         <v>110</v>
       </c>
@@ -2860,8 +2959,8 @@
       <c r="G23" s="18"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="82"/>
-      <c r="B24" s="80"/>
+      <c r="A24" s="88"/>
+      <c r="B24" s="86"/>
       <c r="C24" s="23" t="s">
         <v>111</v>
       </c>
@@ -2873,8 +2972,8 @@
       <c r="G24" s="18"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="82"/>
-      <c r="B25" s="80"/>
+      <c r="A25" s="88"/>
+      <c r="B25" s="86"/>
       <c r="C25" s="23" t="s">
         <v>112</v>
       </c>
@@ -2886,8 +2985,8 @@
       <c r="G25" s="18"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="82"/>
-      <c r="B26" s="80"/>
+      <c r="A26" s="88"/>
+      <c r="B26" s="86"/>
       <c r="C26" s="23" t="s">
         <v>113</v>
       </c>
@@ -2899,8 +2998,8 @@
       <c r="G26" s="18"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="82"/>
-      <c r="B27" s="80"/>
+      <c r="A27" s="88"/>
+      <c r="B27" s="86"/>
       <c r="C27" s="23" t="s">
         <v>114</v>
       </c>
@@ -2912,8 +3011,8 @@
       <c r="G27" s="18"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="82"/>
-      <c r="B28" s="76"/>
+      <c r="A28" s="88"/>
+      <c r="B28" s="82"/>
       <c r="C28" s="23" t="s">
         <v>115</v>
       </c>
@@ -2925,8 +3024,8 @@
       <c r="G28" s="18"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="82"/>
-      <c r="B29" s="84" t="s">
+      <c r="A29" s="88"/>
+      <c r="B29" s="90" t="s">
         <v>116</v>
       </c>
       <c r="C29" s="29" t="s">
@@ -2940,8 +3039,8 @@
       <c r="G29" s="18"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="82"/>
-      <c r="B30" s="85"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="91"/>
       <c r="C30" s="30" t="s">
         <v>118</v>
       </c>
@@ -2953,8 +3052,8 @@
       <c r="G30" s="18"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="82"/>
-      <c r="B31" s="84" t="s">
+      <c r="A31" s="88"/>
+      <c r="B31" s="90" t="s">
         <v>119</v>
       </c>
       <c r="C31" s="32" t="s">
@@ -2968,8 +3067,8 @@
       <c r="G31" s="18"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="82"/>
-      <c r="B32" s="86"/>
+      <c r="A32" s="88"/>
+      <c r="B32" s="92"/>
       <c r="C32" s="32" t="s">
         <v>121</v>
       </c>
@@ -2985,8 +3084,8 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="82"/>
-      <c r="B33" s="86"/>
+      <c r="A33" s="88"/>
+      <c r="B33" s="92"/>
       <c r="C33" s="32" t="s">
         <v>123</v>
       </c>
@@ -2998,8 +3097,8 @@
       <c r="G33" s="17"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="83"/>
-      <c r="B34" s="85"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="91"/>
       <c r="C34" s="32" t="s">
         <v>124</v>
       </c>
@@ -3015,13 +3114,13 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="81" t="s">
+      <c r="A35" s="87" t="s">
         <v>125</v>
       </c>
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="69"/>
+      <c r="C35" s="75"/>
       <c r="D35" s="25">
         <v>321</v>
       </c>
@@ -3032,11 +3131,11 @@
       <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="82"/>
-      <c r="B36" s="67" t="s">
+      <c r="A36" s="88"/>
+      <c r="B36" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="69"/>
+      <c r="C36" s="75"/>
       <c r="D36" s="25">
         <v>87707</v>
       </c>
@@ -3047,11 +3146,11 @@
       <c r="G36" s="18"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="82"/>
-      <c r="B37" s="67" t="s">
+      <c r="A37" s="88"/>
+      <c r="B37" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="69"/>
+      <c r="C37" s="75"/>
       <c r="D37" s="25">
         <v>63519.1</v>
       </c>
@@ -3062,11 +3161,11 @@
       <c r="G37" s="18"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="82"/>
-      <c r="B38" s="67" t="s">
+      <c r="A38" s="88"/>
+      <c r="B38" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="69"/>
+      <c r="C38" s="75"/>
       <c r="D38" s="25">
         <v>36170.99</v>
       </c>
@@ -3077,11 +3176,11 @@
       <c r="G38" s="18"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="82"/>
-      <c r="B39" s="67" t="s">
+      <c r="A39" s="88"/>
+      <c r="B39" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="69"/>
+      <c r="C39" s="75"/>
       <c r="D39" s="25">
         <v>27348.11</v>
       </c>
@@ -3092,11 +3191,11 @@
       <c r="G39" s="18"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="83"/>
-      <c r="B40" s="67" t="s">
+      <c r="A40" s="89"/>
+      <c r="B40" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="C40" s="69"/>
+      <c r="C40" s="75"/>
       <c r="D40" s="25">
         <v>11156</v>
       </c>
@@ -3209,16 +3308,16 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="93" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="93" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="87"/>
-      <c r="B11" s="87"/>
+      <c r="A11" s="93"/>
+      <c r="B11" s="93"/>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="47">

--- a/业务数据统计模板.xlsx
+++ b/业务数据统计模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WasuProject\GitHub\DataStatistic\DataStatistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3C8E6A-BA0F-4F7A-B597-9430E855841A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD918F55-AD54-4D05-B2F8-A579E7684B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="143">
   <si>
     <t>业务模块</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>云存储线上累计收入</t>
-  </si>
-  <si>
-    <t>云存储套餐订购</t>
   </si>
   <si>
     <t>7天事件云存包年</t>
@@ -517,6 +514,14 @@
   </si>
   <si>
     <t>云相册付费用户</t>
+  </si>
+  <si>
+    <t>云存储套餐线上订购</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>云存储套餐线下订购</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -921,7 +926,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1104,6 +1109,15 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1116,22 +1130,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1149,12 +1181,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1164,30 +1190,14 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1463,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13.77734375" customWidth="1"/>
@@ -1495,7 +1505,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.2">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="69" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="37" t="s">
@@ -1510,13 +1520,13 @@
         <v>59014</v>
       </c>
       <c r="E2" s="6">
-        <f t="shared" ref="E2:E39" si="0">(C2-D2)/D2</f>
+        <f t="shared" ref="E2:E43" si="0">(C2-D2)/D2</f>
         <v>6.1138035042532284E-2</v>
       </c>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="16.2">
-      <c r="A3" s="65"/>
+      <c r="A3" s="70"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1533,7 +1543,7 @@
       <c r="F3" s="59"/>
     </row>
     <row r="4" spans="1:6" ht="16.2">
-      <c r="A4" s="65"/>
+      <c r="A4" s="70"/>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1550,7 +1560,7 @@
       <c r="F4" s="60"/>
     </row>
     <row r="5" spans="1:6" ht="16.2">
-      <c r="A5" s="65"/>
+      <c r="A5" s="70"/>
       <c r="B5" s="37" t="s">
         <v>10</v>
       </c>
@@ -1569,7 +1579,7 @@
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="16.2">
-      <c r="A6" s="65"/>
+      <c r="A6" s="70"/>
       <c r="B6" s="37" t="s">
         <v>11</v>
       </c>
@@ -1587,7 +1597,7 @@
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" ht="16.2">
-      <c r="A7" s="65"/>
+      <c r="A7" s="70"/>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1604,9 +1614,9 @@
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" ht="16.2">
-      <c r="A8" s="65"/>
+      <c r="A8" s="70"/>
       <c r="B8" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C8" s="4">
         <v>5682</v>
@@ -1621,9 +1631,9 @@
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" ht="16.2">
-      <c r="A9" s="66"/>
+      <c r="A9" s="71"/>
       <c r="B9" s="61" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C9" s="4">
         <v>5682</v>
@@ -1638,7 +1648,7 @@
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="72" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="39" t="s">
@@ -1658,7 +1668,7 @@
       <c r="F10" s="58"/>
     </row>
     <row r="11" spans="1:6" ht="15">
-      <c r="A11" s="67"/>
+      <c r="A11" s="72"/>
       <c r="B11" s="39" t="s">
         <v>15</v>
       </c>
@@ -1676,7 +1686,7 @@
       <c r="F11" s="58"/>
     </row>
     <row r="12" spans="1:6" ht="15">
-      <c r="A12" s="67"/>
+      <c r="A12" s="72"/>
       <c r="B12" s="48" t="s">
         <v>16</v>
       </c>
@@ -1694,7 +1704,7 @@
       <c r="F12" s="58"/>
     </row>
     <row r="13" spans="1:6" ht="30">
-      <c r="A13" s="66"/>
+      <c r="A13" s="71"/>
       <c r="B13" s="48" t="s">
         <v>17</v>
       </c>
@@ -1712,7 +1722,7 @@
       <c r="F13" s="58"/>
     </row>
     <row r="14" spans="1:6" ht="15">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="39" t="s">
@@ -1733,7 +1743,7 @@
       <c r="F14" s="58"/>
     </row>
     <row r="15" spans="1:6" ht="15">
-      <c r="A15" s="68"/>
+      <c r="A15" s="64"/>
       <c r="B15" s="8" t="s">
         <v>20</v>
       </c>
@@ -1750,7 +1760,7 @@
       <c r="F15" s="58"/>
     </row>
     <row r="16" spans="1:6" ht="15">
-      <c r="A16" s="68"/>
+      <c r="A16" s="64"/>
       <c r="B16" s="8" t="s">
         <v>21</v>
       </c>
@@ -1767,7 +1777,7 @@
       <c r="F16" s="58"/>
     </row>
     <row r="17" spans="1:6" ht="15">
-      <c r="A17" s="68"/>
+      <c r="A17" s="64"/>
       <c r="B17" s="8" t="s">
         <v>22</v>
       </c>
@@ -1784,7 +1794,7 @@
       <c r="F17" s="58"/>
     </row>
     <row r="18" spans="1:6" ht="15">
-      <c r="A18" s="68"/>
+      <c r="A18" s="64"/>
       <c r="B18" s="39" t="s">
         <v>23</v>
       </c>
@@ -1803,7 +1813,7 @@
       <c r="F18" s="58"/>
     </row>
     <row r="19" spans="1:6" ht="15">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="64" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="39" t="s">
@@ -1824,7 +1834,7 @@
       <c r="F19" s="58"/>
     </row>
     <row r="20" spans="1:6" ht="15">
-      <c r="A20" s="68"/>
+      <c r="A20" s="64"/>
       <c r="B20" s="8" t="s">
         <v>26</v>
       </c>
@@ -1841,7 +1851,7 @@
       <c r="F20" s="58"/>
     </row>
     <row r="21" spans="1:6" ht="15">
-      <c r="A21" s="68"/>
+      <c r="A21" s="64"/>
       <c r="B21" s="8" t="s">
         <v>27</v>
       </c>
@@ -1858,7 +1868,7 @@
       <c r="F21" s="58"/>
     </row>
     <row r="22" spans="1:6" ht="15">
-      <c r="A22" s="68"/>
+      <c r="A22" s="64"/>
       <c r="B22" s="8" t="s">
         <v>28</v>
       </c>
@@ -1875,11 +1885,11 @@
       <c r="F22" s="58"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1">
-      <c r="A23" s="69" t="s">
+      <c r="A23" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="39" t="s">
         <v>29</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>30</v>
       </c>
       <c r="C23" s="39">
         <f>业务数据统计!D31</f>
@@ -1895,9 +1905,9 @@
       <c r="F23" s="58"/>
     </row>
     <row r="24" spans="1:6" ht="15">
-      <c r="A24" s="70"/>
+      <c r="A24" s="95"/>
       <c r="B24" s="39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="39">
         <f>业务数据统计!D32-业务数据统计!G32</f>
@@ -1913,7 +1923,7 @@
       <c r="F24" s="58"/>
     </row>
     <row r="25" spans="1:6" ht="15">
-      <c r="A25" s="70"/>
+      <c r="A25" s="95"/>
       <c r="B25" s="39" t="s">
         <v>32</v>
       </c>
@@ -1931,7 +1941,7 @@
       <c r="F25" s="58"/>
     </row>
     <row r="26" spans="1:6" ht="15">
-      <c r="A26" s="70"/>
+      <c r="A26" s="96"/>
       <c r="B26" s="39" t="s">
         <v>33</v>
       </c>
@@ -1949,9 +1959,11 @@
       <c r="F26" s="58"/>
     </row>
     <row r="27" spans="1:6" ht="15">
-      <c r="A27" s="70"/>
+      <c r="A27" s="94" t="s">
+        <v>142</v>
+      </c>
       <c r="B27" s="39" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C27" s="39">
         <f>业务数据统计!D34-业务数据统计!G34</f>
@@ -1967,9 +1979,9 @@
       <c r="F27" s="58"/>
     </row>
     <row r="28" spans="1:6" ht="15">
-      <c r="A28" s="71"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="39" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C28" s="39">
         <f>业务数据统计!G34</f>
@@ -1984,592 +1996,665 @@
       </c>
       <c r="F28" s="58"/>
     </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1">
-      <c r="A29" s="68" t="s">
+    <row r="29" spans="1:6" ht="15">
+      <c r="A29" s="95"/>
+      <c r="B29" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="39">
+        <f>业务数据统计!G34</f>
+        <v>283</v>
+      </c>
+      <c r="D29" s="8">
+        <v>281</v>
+      </c>
+      <c r="E29" s="9">
+        <f t="shared" si="0"/>
+        <v>7.1174377224199285E-3</v>
+      </c>
+      <c r="F29" s="58"/>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" s="95"/>
+      <c r="B30" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="39">
+        <f>业务数据统计!G34</f>
+        <v>283</v>
+      </c>
+      <c r="D30" s="8">
+        <v>281</v>
+      </c>
+      <c r="E30" s="9">
+        <f t="shared" si="0"/>
+        <v>7.1174377224199285E-3</v>
+      </c>
+      <c r="F30" s="58"/>
+    </row>
+    <row r="31" spans="1:6" ht="15">
+      <c r="A31" s="95"/>
+      <c r="B31" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="39">
+        <f>业务数据统计!G34</f>
+        <v>283</v>
+      </c>
+      <c r="D31" s="8">
+        <v>281</v>
+      </c>
+      <c r="E31" s="9">
+        <f t="shared" si="0"/>
+        <v>7.1174377224199285E-3</v>
+      </c>
+      <c r="F31" s="58"/>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" s="96"/>
+      <c r="B32" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="39">
+        <f>业务数据统计!G34</f>
+        <v>283</v>
+      </c>
+      <c r="D32" s="8">
+        <v>281</v>
+      </c>
+      <c r="E32" s="9">
+        <f t="shared" si="0"/>
+        <v>7.1174377224199285E-3</v>
+      </c>
+      <c r="F32" s="58"/>
+    </row>
+    <row r="33" spans="1:7" ht="15" customHeight="1">
+      <c r="A33" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="39">
+      <c r="C33" s="39">
         <f>5859+C20</f>
         <v>6953</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D33" s="8">
         <f>5521+994</f>
         <v>6515</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E33" s="9">
         <f t="shared" si="0"/>
         <v>6.7229470452801227E-2</v>
       </c>
-      <c r="F29" s="58"/>
-    </row>
-    <row r="30" spans="1:6" ht="15">
-      <c r="A30" s="72"/>
-      <c r="B30" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="12">
+      <c r="F33" s="58"/>
+    </row>
+    <row r="34" spans="1:7" ht="15">
+      <c r="A34" s="65"/>
+      <c r="B34" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="12">
         <v>0.46300000000000002</v>
       </c>
-      <c r="D30" s="12">
-        <f>D29/14514</f>
+      <c r="D34" s="12">
+        <f>D33/14514</f>
         <v>0.4488769463965826</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E34" s="13">
         <f t="shared" si="0"/>
         <v>3.1463085188027706E-2</v>
       </c>
-      <c r="F30" s="58"/>
-    </row>
-    <row r="31" spans="1:6" ht="15">
-      <c r="A31" s="72"/>
-      <c r="B31" s="61" t="s">
-        <v>140</v>
-      </c>
-      <c r="C31" s="8">
+      <c r="F34" s="58"/>
+    </row>
+    <row r="35" spans="1:7" ht="15">
+      <c r="A35" s="65"/>
+      <c r="B35" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="8">
         <v>1963</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D35" s="8">
         <v>2114</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E35" s="9">
         <f t="shared" si="0"/>
         <v>-7.1428571428571425E-2</v>
       </c>
-      <c r="F31" s="58"/>
-    </row>
-    <row r="32" spans="1:6" ht="15">
-      <c r="A32" s="72"/>
-      <c r="B32" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="39">
+      <c r="F35" s="58"/>
+    </row>
+    <row r="36" spans="1:7" ht="15">
+      <c r="A36" s="65"/>
+      <c r="B36" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="39">
         <f>业务数据统计!D21</f>
         <v>3615</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D36" s="8">
         <v>3400</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E36" s="9">
         <f t="shared" si="0"/>
         <v>6.3235294117647056E-2</v>
       </c>
-      <c r="F32" s="58"/>
-    </row>
-    <row r="33" spans="1:7" ht="15">
-      <c r="A33" s="72"/>
-      <c r="B33" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="40">
+      <c r="F36" s="58"/>
+    </row>
+    <row r="37" spans="1:7" ht="15">
+      <c r="A37" s="65"/>
+      <c r="B37" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="40">
         <f>C19/C17</f>
         <v>0.49748978897208984</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D37" s="12">
         <f>D19/D17</f>
         <v>0.48975113022867928</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E37" s="9">
         <f t="shared" si="0"/>
         <v>1.5801206502161939E-2</v>
       </c>
-      <c r="F33" s="58"/>
-    </row>
-    <row r="34" spans="1:7" ht="15">
-      <c r="A34" s="72"/>
-      <c r="B34" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="40">
+      <c r="F37" s="58"/>
+    </row>
+    <row r="38" spans="1:7" ht="15">
+      <c r="A38" s="65"/>
+      <c r="B38" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="40">
         <f>业务数据统计!D20/主表!C19</f>
         <v>0.75395535790643975</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D38" s="12">
         <f>8215/D19</f>
         <v>0.73624305431080839</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E38" s="13">
         <f t="shared" si="0"/>
         <v>2.4057685151558702E-2</v>
       </c>
-      <c r="F34" s="58"/>
-    </row>
-    <row r="35" spans="1:7" ht="15">
-      <c r="A35" s="68" t="s">
+      <c r="F38" s="58"/>
+    </row>
+    <row r="39" spans="1:7" ht="15">
+      <c r="A39" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="39">
+      <c r="C39" s="39">
         <f>业务数据统计!D3</f>
         <v>10901</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D39" s="14">
         <v>7295</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E39" s="9">
         <f t="shared" si="0"/>
         <v>0.49431117203564084</v>
       </c>
-      <c r="F35" s="58"/>
-    </row>
-    <row r="36" spans="1:7" ht="15">
-      <c r="A36" s="72"/>
-      <c r="B36" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="39">
+      <c r="F39" s="58"/>
+    </row>
+    <row r="40" spans="1:7" ht="15">
+      <c r="A40" s="65"/>
+      <c r="B40" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="39">
         <f>业务数据统计!D4</f>
         <v>1537</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D40" s="14">
         <v>1458</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E40" s="9">
         <f t="shared" si="0"/>
         <v>5.4183813443072701E-2</v>
       </c>
-      <c r="F36" s="58"/>
-    </row>
-    <row r="37" spans="1:7" ht="15">
-      <c r="A37" s="72"/>
-      <c r="B37" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="39">
+      <c r="F40" s="58"/>
+    </row>
+    <row r="41" spans="1:7" ht="15">
+      <c r="A41" s="65"/>
+      <c r="B41" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="39">
         <f>业务数据统计!D5</f>
         <v>602820</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D41" s="14">
         <v>121740</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E41" s="9">
         <f t="shared" si="0"/>
         <v>3.9517003449975356</v>
       </c>
-      <c r="F37" s="58"/>
-    </row>
-    <row r="38" spans="1:7" ht="15">
-      <c r="A38" s="72"/>
-      <c r="B38" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="39">
+      <c r="F41" s="58"/>
+    </row>
+    <row r="42" spans="1:7" ht="15">
+      <c r="A42" s="65"/>
+      <c r="B42" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="39">
         <f>业务数据统计!D6</f>
         <v>1777</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D42" s="14">
         <v>1735</v>
       </c>
-      <c r="E38" s="9">
-        <f t="shared" ref="E38" si="2">(C38-D38)/D38</f>
+      <c r="E42" s="9">
+        <f t="shared" ref="E42" si="2">(C42-D42)/D42</f>
         <v>2.420749279538905E-2</v>
       </c>
-      <c r="F38" s="58"/>
-      <c r="G38" s="62"/>
-    </row>
-    <row r="39" spans="1:7" ht="15">
-      <c r="A39" s="72"/>
-      <c r="B39" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="C39" s="39">
+      <c r="F42" s="58"/>
+      <c r="G42" s="62"/>
+    </row>
+    <row r="43" spans="1:7" ht="15">
+      <c r="A43" s="65"/>
+      <c r="B43" s="63" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" s="39">
         <v>1856</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D43" s="14">
         <v>1735</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E43" s="9">
         <f t="shared" si="0"/>
         <v>6.9740634005763691E-2</v>
       </c>
-      <c r="F39" s="58"/>
-    </row>
-    <row r="40" spans="1:7" ht="15">
-      <c r="A40" s="68" t="s">
+      <c r="F43" s="58"/>
+    </row>
+    <row r="44" spans="1:7" ht="15">
+      <c r="A44" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="39">
+      <c r="C44" s="39">
         <f>业务数据统计!D16</f>
         <v>1335</v>
       </c>
-      <c r="D40" s="12">
-        <f>C40/C36</f>
+      <c r="D44" s="12">
+        <f>C44/C40</f>
         <v>0.86857514638906963</v>
       </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="58"/>
-    </row>
-    <row r="41" spans="1:7" ht="15">
-      <c r="A41" s="72"/>
-      <c r="B41" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="39">
+      <c r="E44" s="9"/>
+      <c r="F44" s="58"/>
+    </row>
+    <row r="45" spans="1:7" ht="15">
+      <c r="A45" s="65"/>
+      <c r="B45" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="39">
         <f>业务数据统计!D18</f>
         <v>325</v>
       </c>
-      <c r="D41" s="12">
-        <f>C41/C36</f>
+      <c r="D45" s="12">
+        <f>C45/C40</f>
         <v>0.2114508783344177</v>
       </c>
-      <c r="E41" s="9"/>
-      <c r="F41" s="58"/>
-    </row>
-    <row r="42" spans="1:7" ht="15">
-      <c r="A42" s="72"/>
-      <c r="B42" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="39">
+      <c r="E45" s="9"/>
+      <c r="F45" s="58"/>
+    </row>
+    <row r="46" spans="1:7" ht="15">
+      <c r="A46" s="65"/>
+      <c r="B46" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="39">
         <f>业务数据统计!D17</f>
         <v>4</v>
       </c>
-      <c r="D42" s="12">
-        <f>C42/C36</f>
+      <c r="D46" s="12">
+        <f>C46/C40</f>
         <v>2.6024723487312949E-3</v>
       </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="58"/>
-    </row>
-    <row r="43" spans="1:7" ht="15">
-      <c r="A43" s="72"/>
-      <c r="B43" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="39">
+      <c r="E46" s="9"/>
+      <c r="F46" s="58"/>
+    </row>
+    <row r="47" spans="1:7" ht="15">
+      <c r="A47" s="65"/>
+      <c r="B47" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="39">
         <f>业务数据统计!D19</f>
         <v>9</v>
       </c>
-      <c r="D43" s="12">
-        <f>C43/C36</f>
+      <c r="D47" s="12">
+        <f>C47/C40</f>
         <v>5.8555627846454128E-3</v>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="58"/>
-    </row>
-    <row r="44" spans="1:7" ht="15">
-      <c r="A44" s="68" t="s">
+      <c r="E47" s="9"/>
+      <c r="F47" s="58"/>
+    </row>
+    <row r="48" spans="1:7" ht="15">
+      <c r="A48" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="41">
+      <c r="C48" s="41">
         <f>业务数据统计!D35</f>
         <v>321</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D48" s="14">
         <v>321</v>
       </c>
-      <c r="E44" s="9">
-        <f t="shared" ref="E44:E58" si="3">(C44-D44)/D44</f>
+      <c r="E48" s="9">
+        <f t="shared" ref="E48:E62" si="3">(C48-D48)/D48</f>
         <v>0</v>
       </c>
-      <c r="F44" s="58"/>
-    </row>
-    <row r="45" spans="1:7" ht="15">
-      <c r="A45" s="72"/>
-      <c r="B45" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" s="41">
+      <c r="F48" s="58"/>
+    </row>
+    <row r="49" spans="1:6" ht="15">
+      <c r="A49" s="65"/>
+      <c r="B49" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="41">
         <f>业务数据统计!D36</f>
         <v>87707</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D49" s="14">
         <v>79012</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E49" s="9">
         <f t="shared" si="3"/>
         <v>0.11004657520376651</v>
       </c>
-      <c r="F45" s="58"/>
-    </row>
-    <row r="46" spans="1:7" ht="15">
-      <c r="A46" s="72"/>
-      <c r="B46" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="41">
+      <c r="F49" s="58"/>
+    </row>
+    <row r="50" spans="1:6" ht="15">
+      <c r="A50" s="65"/>
+      <c r="B50" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="41">
         <f>业务数据统计!D37</f>
         <v>63519.1</v>
       </c>
-      <c r="D46" s="14">
+      <c r="D50" s="14">
         <v>57685.66</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E50" s="9">
         <f t="shared" si="3"/>
         <v>0.10112461225198767</v>
       </c>
-      <c r="F46" s="58"/>
-    </row>
-    <row r="47" spans="1:7" ht="15">
-      <c r="A47" s="72"/>
-      <c r="B47" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47" s="41">
+      <c r="F50" s="58"/>
+    </row>
+    <row r="51" spans="1:6" ht="15">
+      <c r="A51" s="65"/>
+      <c r="B51" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="41">
         <f>业务数据统计!D38</f>
         <v>36170.99</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D51" s="14">
         <v>32900.660000000003</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E51" s="9">
         <f t="shared" si="3"/>
         <v>9.9400133614340691E-2</v>
       </c>
-      <c r="F47" s="58"/>
-    </row>
-    <row r="48" spans="1:7" ht="15">
-      <c r="A48" s="72"/>
-      <c r="B48" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="41">
+      <c r="F51" s="58"/>
+    </row>
+    <row r="52" spans="1:6" ht="15">
+      <c r="A52" s="65"/>
+      <c r="B52" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="41">
         <f>业务数据统计!D39</f>
         <v>27348.11</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D52" s="14">
         <v>24785</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E52" s="9">
         <f t="shared" si="3"/>
         <v>0.10341375832156549</v>
       </c>
-      <c r="F48" s="58"/>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1">
-      <c r="A49" s="69" t="s">
+      <c r="F52" s="58"/>
+    </row>
+    <row r="53" spans="1:6" ht="15" customHeight="1">
+      <c r="A53" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="B49" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" s="52">
+      <c r="C53" s="52">
         <f>'云相册-城市统计'!B2</f>
         <v>315</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D53" s="15">
         <v>301</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E53" s="9">
         <f t="shared" si="3"/>
         <v>4.6511627906976744E-2</v>
       </c>
-      <c r="F49" s="53" t="str">
+      <c r="F53" s="53" t="str">
         <f>'云相册-城市统计'!A2</f>
         <v>杭州市</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.6">
-      <c r="A50" s="70"/>
-      <c r="B50" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="C50" s="52">
+    <row r="54" spans="1:6" ht="15.6">
+      <c r="A54" s="67"/>
+      <c r="B54" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="52">
         <f>'云相册-城市统计'!B3</f>
         <v>86</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D54" s="16">
         <v>75</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E54" s="9">
         <f t="shared" si="3"/>
         <v>0.14666666666666667</v>
       </c>
-      <c r="F50" s="53" t="str">
+      <c r="F54" s="53" t="str">
         <f>'云相册-城市统计'!A3</f>
         <v>金华市</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15.6">
-      <c r="A51" s="70"/>
-      <c r="B51" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="C51" s="52">
+    <row r="55" spans="1:6" ht="15.6">
+      <c r="A55" s="67"/>
+      <c r="B55" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="52">
         <f>'云相册-城市统计'!B4</f>
         <v>55</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D55" s="16">
         <v>54</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E55" s="9">
         <f t="shared" si="3"/>
         <v>1.8518518518518517E-2</v>
       </c>
-      <c r="F51" s="53" t="str">
+      <c r="F55" s="53" t="str">
         <f>'云相册-城市统计'!A4</f>
         <v>绍兴市</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.6">
-      <c r="A52" s="70"/>
-      <c r="B52" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="C52" s="52">
+    <row r="56" spans="1:6" ht="15.6">
+      <c r="A56" s="67"/>
+      <c r="B56" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="52">
         <f>'云相册-城市统计'!B5</f>
         <v>49</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D56" s="16">
         <v>46</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E56" s="9">
         <f t="shared" si="3"/>
         <v>6.5217391304347824E-2</v>
       </c>
-      <c r="F52" s="53" t="str">
+      <c r="F56" s="53" t="str">
         <f>'云相册-城市统计'!A5</f>
         <v>湖州市</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.6">
-      <c r="A53" s="70"/>
-      <c r="B53" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="C53" s="52">
+    <row r="57" spans="1:6" ht="15.6">
+      <c r="A57" s="67"/>
+      <c r="B57" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="52">
         <f>'云相册-城市统计'!B6</f>
         <v>46</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D57" s="16">
         <v>40</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E57" s="9">
         <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
-      <c r="F53" s="53" t="str">
+      <c r="F57" s="53" t="str">
         <f>'云相册-城市统计'!A6</f>
         <v>衢州市</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.6">
-      <c r="A54" s="70"/>
-      <c r="B54" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="C54" s="52">
+    <row r="58" spans="1:6" ht="15.6">
+      <c r="A58" s="67"/>
+      <c r="B58" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" s="52">
         <f>'云相册-城市统计'!B7</f>
         <v>45</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D58" s="16">
         <v>43</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E58" s="9">
         <f t="shared" si="3"/>
         <v>4.6511627906976744E-2</v>
       </c>
-      <c r="F54" s="53" t="str">
+      <c r="F58" s="53" t="str">
         <f>'云相册-城市统计'!A7</f>
         <v>嘉兴市</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.6">
-      <c r="A55" s="70"/>
-      <c r="B55" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C55" s="52">
+    <row r="59" spans="1:6" ht="15.6">
+      <c r="A59" s="67"/>
+      <c r="B59" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59" s="52">
         <f>'云相册-城市统计'!B8</f>
         <v>35</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D59" s="16">
         <v>35</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E59" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F55" s="53" t="str">
+      <c r="F59" s="53" t="str">
         <f>'云相册-城市统计'!A8</f>
         <v>上海市</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.6">
-      <c r="A56" s="70"/>
-      <c r="B56" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" s="52">
+    <row r="60" spans="1:6" ht="15.6">
+      <c r="A60" s="67"/>
+      <c r="B60" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60" s="52">
         <f>'云相册-城市统计'!B9</f>
         <v>33</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D60" s="16">
         <v>33</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E60" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F56" s="53" t="str">
+      <c r="F60" s="53" t="str">
         <f>'云相册-城市统计'!A9</f>
         <v>温州市</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.6">
-      <c r="A57" s="70"/>
-      <c r="B57" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C57" s="52">
+    <row r="61" spans="1:6" ht="15.6">
+      <c r="A61" s="67"/>
+      <c r="B61" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" s="52">
         <f>'云相册-城市统计'!B10</f>
         <v>33</v>
       </c>
-      <c r="D57" s="16">
+      <c r="D61" s="16">
         <v>31</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E61" s="9">
         <f t="shared" si="3"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="F57" s="53" t="str">
+      <c r="F61" s="53" t="str">
         <f>'云相册-城市统计'!A10</f>
         <v>六安市</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.6">
-      <c r="A58" s="71"/>
-      <c r="B58" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C58" s="52">
+    <row r="62" spans="1:6" ht="15.6">
+      <c r="A62" s="68"/>
+      <c r="B62" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" s="52">
         <f>'云相册-城市统计'!B11</f>
         <v>32</v>
       </c>
-      <c r="D58" s="16">
+      <c r="D62" s="16">
         <v>31</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E62" s="9">
         <f t="shared" si="3"/>
         <v>3.2258064516129031E-2</v>
       </c>
-      <c r="F58" s="53" t="str">
+      <c r="F62" s="53" t="str">
         <f>'云相册-城市统计'!A11</f>
         <v>宁波市</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A29:A34"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="A44:A48"/>
-    <mergeCell ref="A49:A58"/>
+  <mergeCells count="11">
     <mergeCell ref="A2:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="A48:A52"/>
+    <mergeCell ref="A53:A62"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2587,34 +2672,34 @@
   <sheetData>
     <row r="1" spans="1:2" ht="95.4" customHeight="1">
       <c r="A1" s="55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1" s="56" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="57" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2639,26 +2724,26 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="73" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="75"/>
+        <v>78</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="74"/>
       <c r="E1" s="18"/>
       <c r="F1" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="19" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1">
+      <c r="A2" s="85" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="B2" s="86"/>
+      <c r="C2" s="20" t="s">
         <v>82</v>
-      </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="20" t="s">
-        <v>83</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="18"/>
@@ -2670,14 +2755,14 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="78" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="81" t="s">
+      <c r="A3" s="87" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>84</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>85</v>
       </c>
       <c r="D3" s="23">
         <v>10901</v>
@@ -2687,10 +2772,10 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="79"/>
-      <c r="B4" s="82"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="80"/>
       <c r="C4" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" s="23">
         <v>1537</v>
@@ -2700,12 +2785,12 @@
       <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="79"/>
-      <c r="B5" s="81" t="s">
+      <c r="A5" s="88"/>
+      <c r="B5" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>86</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>87</v>
       </c>
       <c r="D5" s="23">
         <v>602820</v>
@@ -2715,10 +2800,10 @@
       <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="79"/>
-      <c r="B6" s="82"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="80"/>
       <c r="C6" s="24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D6" s="24">
         <v>1777</v>
@@ -2728,12 +2813,12 @@
       <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="79"/>
-      <c r="B7" s="83" t="s">
+      <c r="A7" s="88"/>
+      <c r="B7" s="90" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>89</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>90</v>
       </c>
       <c r="D7" s="26">
         <v>441</v>
@@ -2743,10 +2828,10 @@
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="79"/>
-      <c r="B8" s="84"/>
+      <c r="A8" s="88"/>
+      <c r="B8" s="91"/>
       <c r="C8" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" s="27">
         <v>31</v>
@@ -2756,10 +2841,10 @@
       <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="79"/>
-      <c r="B9" s="84"/>
+      <c r="A9" s="88"/>
+      <c r="B9" s="91"/>
       <c r="C9" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D9" s="25">
         <v>14</v>
@@ -2769,10 +2854,10 @@
       <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="79"/>
-      <c r="B10" s="85"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="92"/>
       <c r="C10" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D10" s="25">
         <v>7</v>
@@ -2782,12 +2867,12 @@
       <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="79"/>
-      <c r="B11" s="83" t="s">
+      <c r="A11" s="88"/>
+      <c r="B11" s="90" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>94</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>95</v>
       </c>
       <c r="D11" s="25">
         <v>468</v>
@@ -2797,10 +2882,10 @@
       <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="79"/>
-      <c r="B12" s="84"/>
+      <c r="A12" s="88"/>
+      <c r="B12" s="91"/>
       <c r="C12" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" s="25">
         <v>186</v>
@@ -2810,10 +2895,10 @@
       <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="79"/>
-      <c r="B13" s="84"/>
+      <c r="A13" s="88"/>
+      <c r="B13" s="91"/>
       <c r="C13" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" s="25">
         <v>89</v>
@@ -2823,10 +2908,10 @@
       <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="79"/>
-      <c r="B14" s="85"/>
+      <c r="A14" s="88"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D14" s="25">
         <v>380</v>
@@ -2836,25 +2921,25 @@
       <c r="G14" s="18"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="79"/>
-      <c r="B15" s="81" t="s">
+      <c r="A15" s="88"/>
+      <c r="B15" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="D15" s="23" t="s">
         <v>100</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>101</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="79"/>
-      <c r="B16" s="86"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="79"/>
       <c r="C16" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" s="23">
         <v>1335</v>
@@ -2864,10 +2949,10 @@
       <c r="G16" s="18"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="79"/>
-      <c r="B17" s="86"/>
+      <c r="A17" s="88"/>
+      <c r="B17" s="79"/>
       <c r="C17" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" s="23">
         <v>4</v>
@@ -2877,10 +2962,10 @@
       <c r="G17" s="18"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="79"/>
-      <c r="B18" s="86"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="79"/>
       <c r="C18" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D18" s="23">
         <v>325</v>
@@ -2890,10 +2975,10 @@
       <c r="G18" s="18"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="80"/>
-      <c r="B19" s="82"/>
+      <c r="A19" s="89"/>
+      <c r="B19" s="80"/>
       <c r="C19" s="28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" s="28">
         <v>9</v>
@@ -2903,14 +2988,14 @@
       <c r="G19" s="18"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="75" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="C20" s="20" t="s">
         <v>107</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>108</v>
       </c>
       <c r="D20" s="23">
         <v>8816</v>
@@ -2920,10 +3005,10 @@
       <c r="G20" s="18"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="88"/>
-      <c r="B21" s="86"/>
+      <c r="A21" s="76"/>
+      <c r="B21" s="79"/>
       <c r="C21" s="20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="23">
         <v>3615</v>
@@ -2933,10 +3018,10 @@
       <c r="G21" s="18"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="88"/>
-      <c r="B22" s="86"/>
+      <c r="A22" s="76"/>
+      <c r="B22" s="79"/>
       <c r="C22" s="23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D22" s="23">
         <v>22</v>
@@ -2946,10 +3031,10 @@
       <c r="G22" s="18"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="88"/>
-      <c r="B23" s="86"/>
+      <c r="A23" s="76"/>
+      <c r="B23" s="79"/>
       <c r="C23" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" s="23">
         <v>836</v>
@@ -2959,10 +3044,10 @@
       <c r="G23" s="18"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="88"/>
-      <c r="B24" s="86"/>
+      <c r="A24" s="76"/>
+      <c r="B24" s="79"/>
       <c r="C24" s="23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D24" s="23">
         <v>2165</v>
@@ -2972,10 +3057,10 @@
       <c r="G24" s="18"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="88"/>
-      <c r="B25" s="86"/>
+      <c r="A25" s="76"/>
+      <c r="B25" s="79"/>
       <c r="C25" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D25" s="23">
         <v>1079</v>
@@ -2985,51 +3070,51 @@
       <c r="G25" s="18"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="88"/>
-      <c r="B26" s="86"/>
+      <c r="A26" s="76"/>
+      <c r="B26" s="79"/>
       <c r="C26" s="23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="88"/>
-      <c r="B27" s="86"/>
+      <c r="A27" s="76"/>
+      <c r="B27" s="79"/>
       <c r="C27" s="23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="88"/>
-      <c r="B28" s="82"/>
+      <c r="A28" s="76"/>
+      <c r="B28" s="80"/>
       <c r="C28" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="88"/>
-      <c r="B29" s="90" t="s">
+      <c r="A29" s="76"/>
+      <c r="B29" s="81" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="29" t="s">
         <v>116</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>117</v>
       </c>
       <c r="D29" s="29">
         <v>13036</v>
@@ -3039,25 +3124,25 @@
       <c r="G29" s="18"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="88"/>
-      <c r="B30" s="91"/>
+      <c r="A30" s="76"/>
+      <c r="B30" s="82"/>
       <c r="C30" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="88"/>
-      <c r="B31" s="90" t="s">
+      <c r="A31" s="76"/>
+      <c r="B31" s="81" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="32" t="s">
         <v>119</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>120</v>
       </c>
       <c r="D31" s="32">
         <v>1465</v>
@@ -3067,27 +3152,27 @@
       <c r="G31" s="18"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="88"/>
-      <c r="B32" s="92"/>
+      <c r="A32" s="76"/>
+      <c r="B32" s="83"/>
       <c r="C32" s="32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D32" s="32">
         <v>6846</v>
       </c>
       <c r="E32" s="18"/>
       <c r="F32" s="33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G32" s="25">
         <v>6801</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="88"/>
-      <c r="B33" s="92"/>
+      <c r="A33" s="76"/>
+      <c r="B33" s="83"/>
       <c r="C33" s="32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D33" s="32">
         <v>190</v>
@@ -3097,30 +3182,30 @@
       <c r="G33" s="17"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="89"/>
-      <c r="B34" s="91"/>
+      <c r="A34" s="77"/>
+      <c r="B34" s="82"/>
       <c r="C34" s="32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D34" s="32">
         <v>288</v>
       </c>
       <c r="E34" s="18"/>
       <c r="F34" s="33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G34" s="25">
         <v>283</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="87" t="s">
-        <v>125</v>
+      <c r="A35" s="75" t="s">
+        <v>124</v>
       </c>
       <c r="B35" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="75"/>
+        <v>52</v>
+      </c>
+      <c r="C35" s="74"/>
       <c r="D35" s="25">
         <v>321</v>
       </c>
@@ -3131,11 +3216,11 @@
       <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="88"/>
+      <c r="A36" s="76"/>
       <c r="B36" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="75"/>
+        <v>53</v>
+      </c>
+      <c r="C36" s="74"/>
       <c r="D36" s="25">
         <v>87707</v>
       </c>
@@ -3146,11 +3231,11 @@
       <c r="G36" s="18"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="88"/>
+      <c r="A37" s="76"/>
       <c r="B37" s="73" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="75"/>
+        <v>54</v>
+      </c>
+      <c r="C37" s="74"/>
       <c r="D37" s="25">
         <v>63519.1</v>
       </c>
@@ -3161,11 +3246,11 @@
       <c r="G37" s="18"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="88"/>
+      <c r="A38" s="76"/>
       <c r="B38" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="75"/>
+        <v>55</v>
+      </c>
+      <c r="C38" s="74"/>
       <c r="D38" s="25">
         <v>36170.99</v>
       </c>
@@ -3176,11 +3261,11 @@
       <c r="G38" s="18"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="88"/>
+      <c r="A39" s="76"/>
       <c r="B39" s="73" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="75"/>
+        <v>56</v>
+      </c>
+      <c r="C39" s="74"/>
       <c r="D39" s="25">
         <v>27348.11</v>
       </c>
@@ -3191,11 +3276,11 @@
       <c r="G39" s="18"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="89"/>
+      <c r="A40" s="77"/>
       <c r="B40" s="73" t="s">
-        <v>126</v>
-      </c>
-      <c r="C40" s="75"/>
+        <v>125</v>
+      </c>
+      <c r="C40" s="74"/>
       <c r="D40" s="25">
         <v>11156</v>
       </c>
@@ -3207,6 +3292,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:A19"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="B15:B19"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="A20:A34"/>
     <mergeCell ref="B20:B28"/>
@@ -3218,14 +3311,6 @@
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:A19"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="B15:B19"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3300,7 +3385,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" s="45">
         <f>AVERAGE(B1:B7)</f>
@@ -3309,10 +3394,10 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="93" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="93" t="s">
         <v>128</v>
-      </c>
-      <c r="B10" s="93" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3348,15 +3433,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="50" t="s">
         <v>130</v>
-      </c>
-      <c r="B1" s="50" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4">
       <c r="A2" s="51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="51">
         <v>315</v>
@@ -3364,7 +3449,7 @@
     </row>
     <row r="3" spans="1:2" ht="14.4">
       <c r="A3" s="51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" s="51">
         <v>86</v>
@@ -3372,7 +3457,7 @@
     </row>
     <row r="4" spans="1:2" ht="14.4">
       <c r="A4" s="51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="51">
         <v>55</v>
@@ -3380,7 +3465,7 @@
     </row>
     <row r="5" spans="1:2" ht="14.4">
       <c r="A5" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="51">
         <v>49</v>
@@ -3388,7 +3473,7 @@
     </row>
     <row r="6" spans="1:2" ht="14.4">
       <c r="A6" s="51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" s="51">
         <v>46</v>
@@ -3396,7 +3481,7 @@
     </row>
     <row r="7" spans="1:2" ht="14.4">
       <c r="A7" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7" s="51">
         <v>45</v>
@@ -3404,7 +3489,7 @@
     </row>
     <row r="8" spans="1:2" ht="14.4">
       <c r="A8" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="51">
         <v>35</v>
@@ -3412,7 +3497,7 @@
     </row>
     <row r="9" spans="1:2" ht="14.4">
       <c r="A9" s="51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="51">
         <v>33</v>
@@ -3420,7 +3505,7 @@
     </row>
     <row r="10" spans="1:2" ht="14.4">
       <c r="A10" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="51">
         <v>33</v>
@@ -3428,7 +3513,7 @@
     </row>
     <row r="11" spans="1:2" ht="14.4">
       <c r="A11" s="51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="51">
         <v>32</v>

--- a/业务数据统计模板.xlsx
+++ b/业务数据统计模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WasuProject\GitHub\DataStatistic\DataStatistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD918F55-AD54-4D05-B2F8-A579E7684B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EC9236-7B84-40AB-9BB2-229A8951E479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="147">
   <si>
     <t>业务模块</t>
   </si>
@@ -111,24 +111,6 @@
   </si>
   <si>
     <t>云存储线上累计收入</t>
-  </si>
-  <si>
-    <t>7天事件云存包年</t>
-  </si>
-  <si>
-    <t>7天事件单月订购</t>
-  </si>
-  <si>
-    <t>7天事件云存连续包月</t>
-  </si>
-  <si>
-    <t>7天全时段包年</t>
-  </si>
-  <si>
-    <t>7天全时段单月订购</t>
-  </si>
-  <si>
-    <t>7天全时段连续包月</t>
   </si>
   <si>
     <t>云存储用户使用情况</t>
@@ -521,6 +503,46 @@
   </si>
   <si>
     <t>云存储套餐线下订购</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天事件云存包年（线下）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天事件云存包年（线上）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天事件单月订购（线上）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天全时段包年（线上）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天全时段单月订购（线上）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天事件单月订购（线下）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天事件云存连续包月（线下）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天全时段包年（线下）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天全时段单月订购（线下）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>7天全时段连续包月（线下）</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -926,7 +948,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1109,31 +1131,70 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1143,15 +1204,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1163,41 +1215,9 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1505,7 +1525,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.2">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="64" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="37" t="s">
@@ -1526,7 +1546,7 @@
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="16.2">
-      <c r="A3" s="70"/>
+      <c r="A3" s="65"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1543,7 +1563,7 @@
       <c r="F3" s="59"/>
     </row>
     <row r="4" spans="1:6" ht="16.2">
-      <c r="A4" s="70"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1560,7 +1580,7 @@
       <c r="F4" s="60"/>
     </row>
     <row r="5" spans="1:6" ht="16.2">
-      <c r="A5" s="70"/>
+      <c r="A5" s="65"/>
       <c r="B5" s="37" t="s">
         <v>10</v>
       </c>
@@ -1579,7 +1599,7 @@
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="16.2">
-      <c r="A6" s="70"/>
+      <c r="A6" s="65"/>
       <c r="B6" s="37" t="s">
         <v>11</v>
       </c>
@@ -1597,7 +1617,7 @@
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" ht="16.2">
-      <c r="A7" s="70"/>
+      <c r="A7" s="65"/>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1614,9 +1634,9 @@
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" ht="16.2">
-      <c r="A8" s="70"/>
+      <c r="A8" s="65"/>
       <c r="B8" s="61" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C8" s="4">
         <v>5682</v>
@@ -1631,9 +1651,9 @@
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" ht="16.2">
-      <c r="A9" s="71"/>
+      <c r="A9" s="66"/>
       <c r="B9" s="61" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C9" s="4">
         <v>5682</v>
@@ -1648,7 +1668,7 @@
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="67" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="39" t="s">
@@ -1668,7 +1688,7 @@
       <c r="F10" s="58"/>
     </row>
     <row r="11" spans="1:6" ht="15">
-      <c r="A11" s="72"/>
+      <c r="A11" s="67"/>
       <c r="B11" s="39" t="s">
         <v>15</v>
       </c>
@@ -1686,7 +1706,7 @@
       <c r="F11" s="58"/>
     </row>
     <row r="12" spans="1:6" ht="15">
-      <c r="A12" s="72"/>
+      <c r="A12" s="67"/>
       <c r="B12" s="48" t="s">
         <v>16</v>
       </c>
@@ -1704,7 +1724,7 @@
       <c r="F12" s="58"/>
     </row>
     <row r="13" spans="1:6" ht="30">
-      <c r="A13" s="71"/>
+      <c r="A13" s="66"/>
       <c r="B13" s="48" t="s">
         <v>17</v>
       </c>
@@ -1722,7 +1742,7 @@
       <c r="F13" s="58"/>
     </row>
     <row r="14" spans="1:6" ht="15">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="68" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="39" t="s">
@@ -1743,7 +1763,7 @@
       <c r="F14" s="58"/>
     </row>
     <row r="15" spans="1:6" ht="15">
-      <c r="A15" s="64"/>
+      <c r="A15" s="68"/>
       <c r="B15" s="8" t="s">
         <v>20</v>
       </c>
@@ -1760,7 +1780,7 @@
       <c r="F15" s="58"/>
     </row>
     <row r="16" spans="1:6" ht="15">
-      <c r="A16" s="64"/>
+      <c r="A16" s="68"/>
       <c r="B16" s="8" t="s">
         <v>21</v>
       </c>
@@ -1777,7 +1797,7 @@
       <c r="F16" s="58"/>
     </row>
     <row r="17" spans="1:6" ht="15">
-      <c r="A17" s="64"/>
+      <c r="A17" s="68"/>
       <c r="B17" s="8" t="s">
         <v>22</v>
       </c>
@@ -1794,7 +1814,7 @@
       <c r="F17" s="58"/>
     </row>
     <row r="18" spans="1:6" ht="15">
-      <c r="A18" s="64"/>
+      <c r="A18" s="68"/>
       <c r="B18" s="39" t="s">
         <v>23</v>
       </c>
@@ -1813,7 +1833,7 @@
       <c r="F18" s="58"/>
     </row>
     <row r="19" spans="1:6" ht="15">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="68" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="39" t="s">
@@ -1834,7 +1854,7 @@
       <c r="F19" s="58"/>
     </row>
     <row r="20" spans="1:6" ht="15">
-      <c r="A20" s="64"/>
+      <c r="A20" s="68"/>
       <c r="B20" s="8" t="s">
         <v>26</v>
       </c>
@@ -1851,7 +1871,7 @@
       <c r="F20" s="58"/>
     </row>
     <row r="21" spans="1:6" ht="15">
-      <c r="A21" s="64"/>
+      <c r="A21" s="68"/>
       <c r="B21" s="8" t="s">
         <v>27</v>
       </c>
@@ -1868,7 +1888,7 @@
       <c r="F21" s="58"/>
     </row>
     <row r="22" spans="1:6" ht="15">
-      <c r="A22" s="64"/>
+      <c r="A22" s="68"/>
       <c r="B22" s="8" t="s">
         <v>28</v>
       </c>
@@ -1884,12 +1904,12 @@
       </c>
       <c r="F22" s="58"/>
     </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1">
-      <c r="A23" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>29</v>
+    <row r="23" spans="1:6" ht="30">
+      <c r="A23" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>138</v>
       </c>
       <c r="C23" s="39">
         <f>业务数据统计!D31</f>
@@ -1904,10 +1924,10 @@
       </c>
       <c r="F23" s="58"/>
     </row>
-    <row r="24" spans="1:6" ht="15">
-      <c r="A24" s="95"/>
-      <c r="B24" s="39" t="s">
-        <v>30</v>
+    <row r="24" spans="1:6" ht="30">
+      <c r="A24" s="70"/>
+      <c r="B24" s="63" t="s">
+        <v>139</v>
       </c>
       <c r="C24" s="39">
         <f>业务数据统计!D32-业务数据统计!G32</f>
@@ -1922,10 +1942,10 @@
       </c>
       <c r="F24" s="58"/>
     </row>
-    <row r="25" spans="1:6" ht="15">
-      <c r="A25" s="95"/>
-      <c r="B25" s="39" t="s">
-        <v>32</v>
+    <row r="25" spans="1:6" ht="30">
+      <c r="A25" s="70"/>
+      <c r="B25" s="63" t="s">
+        <v>140</v>
       </c>
       <c r="C25" s="39">
         <f>业务数据统计!G32</f>
@@ -1940,10 +1960,10 @@
       </c>
       <c r="F25" s="58"/>
     </row>
-    <row r="26" spans="1:6" ht="15">
-      <c r="A26" s="96"/>
-      <c r="B26" s="39" t="s">
-        <v>33</v>
+    <row r="26" spans="1:6" ht="30">
+      <c r="A26" s="71"/>
+      <c r="B26" s="63" t="s">
+        <v>141</v>
       </c>
       <c r="C26" s="39">
         <f>业务数据统计!D33</f>
@@ -1958,12 +1978,12 @@
       </c>
       <c r="F26" s="58"/>
     </row>
-    <row r="27" spans="1:6" ht="15">
-      <c r="A27" s="94" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>29</v>
+    <row r="27" spans="1:6" ht="30">
+      <c r="A27" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>137</v>
       </c>
       <c r="C27" s="39">
         <f>业务数据统计!D34-业务数据统计!G34</f>
@@ -1978,10 +1998,10 @@
       </c>
       <c r="F27" s="58"/>
     </row>
-    <row r="28" spans="1:6" ht="15">
-      <c r="A28" s="95"/>
-      <c r="B28" s="39" t="s">
-        <v>30</v>
+    <row r="28" spans="1:6" ht="30">
+      <c r="A28" s="70"/>
+      <c r="B28" s="63" t="s">
+        <v>142</v>
       </c>
       <c r="C28" s="39">
         <f>业务数据统计!G34</f>
@@ -1996,10 +2016,10 @@
       </c>
       <c r="F28" s="58"/>
     </row>
-    <row r="29" spans="1:6" ht="15">
-      <c r="A29" s="95"/>
-      <c r="B29" s="39" t="s">
-        <v>31</v>
+    <row r="29" spans="1:6" ht="30">
+      <c r="A29" s="70"/>
+      <c r="B29" s="63" t="s">
+        <v>143</v>
       </c>
       <c r="C29" s="39">
         <f>业务数据统计!G34</f>
@@ -2014,10 +2034,10 @@
       </c>
       <c r="F29" s="58"/>
     </row>
-    <row r="30" spans="1:6" ht="15">
-      <c r="A30" s="95"/>
-      <c r="B30" s="39" t="s">
-        <v>32</v>
+    <row r="30" spans="1:6" ht="30">
+      <c r="A30" s="70"/>
+      <c r="B30" s="63" t="s">
+        <v>144</v>
       </c>
       <c r="C30" s="39">
         <f>业务数据统计!G34</f>
@@ -2032,10 +2052,10 @@
       </c>
       <c r="F30" s="58"/>
     </row>
-    <row r="31" spans="1:6" ht="15">
-      <c r="A31" s="95"/>
-      <c r="B31" s="39" t="s">
-        <v>33</v>
+    <row r="31" spans="1:6" ht="30">
+      <c r="A31" s="70"/>
+      <c r="B31" s="63" t="s">
+        <v>145</v>
       </c>
       <c r="C31" s="39">
         <f>业务数据统计!G34</f>
@@ -2050,10 +2070,10 @@
       </c>
       <c r="F31" s="58"/>
     </row>
-    <row r="32" spans="1:6" ht="15">
-      <c r="A32" s="96"/>
-      <c r="B32" s="39" t="s">
-        <v>34</v>
+    <row r="32" spans="1:6" ht="30">
+      <c r="A32" s="71"/>
+      <c r="B32" s="63" t="s">
+        <v>146</v>
       </c>
       <c r="C32" s="39">
         <f>业务数据统计!G34</f>
@@ -2069,11 +2089,11 @@
       <c r="F32" s="58"/>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1">
-      <c r="A33" s="64" t="s">
-        <v>35</v>
+      <c r="A33" s="68" t="s">
+        <v>29</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C33" s="39">
         <f>5859+C20</f>
@@ -2090,9 +2110,9 @@
       <c r="F33" s="58"/>
     </row>
     <row r="34" spans="1:7" ht="15">
-      <c r="A34" s="65"/>
+      <c r="A34" s="72"/>
       <c r="B34" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C34" s="12">
         <v>0.46300000000000002</v>
@@ -2108,9 +2128,9 @@
       <c r="F34" s="58"/>
     </row>
     <row r="35" spans="1:7" ht="15">
-      <c r="A35" s="65"/>
+      <c r="A35" s="72"/>
       <c r="B35" s="61" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C35" s="8">
         <v>1963</v>
@@ -2125,9 +2145,9 @@
       <c r="F35" s="58"/>
     </row>
     <row r="36" spans="1:7" ht="15">
-      <c r="A36" s="65"/>
+      <c r="A36" s="72"/>
       <c r="B36" s="39" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C36" s="39">
         <f>业务数据统计!D21</f>
@@ -2143,9 +2163,9 @@
       <c r="F36" s="58"/>
     </row>
     <row r="37" spans="1:7" ht="15">
-      <c r="A37" s="65"/>
+      <c r="A37" s="72"/>
       <c r="B37" s="39" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C37" s="40">
         <f>C19/C17</f>
@@ -2162,9 +2182,9 @@
       <c r="F37" s="58"/>
     </row>
     <row r="38" spans="1:7" ht="15">
-      <c r="A38" s="65"/>
+      <c r="A38" s="72"/>
       <c r="B38" s="39" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C38" s="40">
         <f>业务数据统计!D20/主表!C19</f>
@@ -2181,11 +2201,11 @@
       <c r="F38" s="58"/>
     </row>
     <row r="39" spans="1:7" ht="15">
-      <c r="A39" s="64" t="s">
-        <v>41</v>
+      <c r="A39" s="68" t="s">
+        <v>35</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C39" s="39">
         <f>业务数据统计!D3</f>
@@ -2201,9 +2221,9 @@
       <c r="F39" s="58"/>
     </row>
     <row r="40" spans="1:7" ht="15">
-      <c r="A40" s="65"/>
+      <c r="A40" s="72"/>
       <c r="B40" s="39" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C40" s="39">
         <f>业务数据统计!D4</f>
@@ -2219,9 +2239,9 @@
       <c r="F40" s="58"/>
     </row>
     <row r="41" spans="1:7" ht="15">
-      <c r="A41" s="65"/>
+      <c r="A41" s="72"/>
       <c r="B41" s="39" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C41" s="39">
         <f>业务数据统计!D5</f>
@@ -2237,9 +2257,9 @@
       <c r="F41" s="58"/>
     </row>
     <row r="42" spans="1:7" ht="15">
-      <c r="A42" s="65"/>
+      <c r="A42" s="72"/>
       <c r="B42" s="39" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C42" s="39">
         <f>业务数据统计!D6</f>
@@ -2256,9 +2276,9 @@
       <c r="G42" s="62"/>
     </row>
     <row r="43" spans="1:7" ht="15">
-      <c r="A43" s="65"/>
+      <c r="A43" s="72"/>
       <c r="B43" s="63" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C43" s="39">
         <v>1856</v>
@@ -2273,11 +2293,11 @@
       <c r="F43" s="58"/>
     </row>
     <row r="44" spans="1:7" ht="15">
-      <c r="A44" s="64" t="s">
-        <v>46</v>
+      <c r="A44" s="68" t="s">
+        <v>40</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C44" s="39">
         <f>业务数据统计!D16</f>
@@ -2291,9 +2311,9 @@
       <c r="F44" s="58"/>
     </row>
     <row r="45" spans="1:7" ht="15">
-      <c r="A45" s="65"/>
+      <c r="A45" s="72"/>
       <c r="B45" s="39" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C45" s="39">
         <f>业务数据统计!D18</f>
@@ -2307,9 +2327,9 @@
       <c r="F45" s="58"/>
     </row>
     <row r="46" spans="1:7" ht="15">
-      <c r="A46" s="65"/>
+      <c r="A46" s="72"/>
       <c r="B46" s="39" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C46" s="39">
         <f>业务数据统计!D17</f>
@@ -2323,9 +2343,9 @@
       <c r="F46" s="58"/>
     </row>
     <row r="47" spans="1:7" ht="15">
-      <c r="A47" s="65"/>
+      <c r="A47" s="72"/>
       <c r="B47" s="39" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C47" s="39">
         <f>业务数据统计!D19</f>
@@ -2339,11 +2359,11 @@
       <c r="F47" s="58"/>
     </row>
     <row r="48" spans="1:7" ht="15">
-      <c r="A48" s="64" t="s">
-        <v>51</v>
+      <c r="A48" s="68" t="s">
+        <v>45</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C48" s="41">
         <f>业务数据统计!D35</f>
@@ -2359,9 +2379,9 @@
       <c r="F48" s="58"/>
     </row>
     <row r="49" spans="1:6" ht="15">
-      <c r="A49" s="65"/>
+      <c r="A49" s="72"/>
       <c r="B49" s="39" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C49" s="41">
         <f>业务数据统计!D36</f>
@@ -2377,9 +2397,9 @@
       <c r="F49" s="58"/>
     </row>
     <row r="50" spans="1:6" ht="15">
-      <c r="A50" s="65"/>
+      <c r="A50" s="72"/>
       <c r="B50" s="39" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C50" s="41">
         <f>业务数据统计!D37</f>
@@ -2395,9 +2415,9 @@
       <c r="F50" s="58"/>
     </row>
     <row r="51" spans="1:6" ht="15">
-      <c r="A51" s="65"/>
+      <c r="A51" s="72"/>
       <c r="B51" s="39" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C51" s="41">
         <f>业务数据统计!D38</f>
@@ -2413,9 +2433,9 @@
       <c r="F51" s="58"/>
     </row>
     <row r="52" spans="1:6" ht="15">
-      <c r="A52" s="65"/>
+      <c r="A52" s="72"/>
       <c r="B52" s="39" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C52" s="41">
         <f>业务数据统计!D39</f>
@@ -2431,11 +2451,11 @@
       <c r="F52" s="58"/>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1">
-      <c r="A53" s="66" t="s">
-        <v>57</v>
+      <c r="A53" s="73" t="s">
+        <v>51</v>
       </c>
       <c r="B53" s="39" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C53" s="52">
         <f>'云相册-城市统计'!B2</f>
@@ -2454,9 +2474,9 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.6">
-      <c r="A54" s="67"/>
+      <c r="A54" s="70"/>
       <c r="B54" s="39" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C54" s="52">
         <f>'云相册-城市统计'!B3</f>
@@ -2475,9 +2495,9 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.6">
-      <c r="A55" s="67"/>
+      <c r="A55" s="70"/>
       <c r="B55" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C55" s="52">
         <f>'云相册-城市统计'!B4</f>
@@ -2496,9 +2516,9 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.6">
-      <c r="A56" s="67"/>
+      <c r="A56" s="70"/>
       <c r="B56" s="39" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C56" s="52">
         <f>'云相册-城市统计'!B5</f>
@@ -2517,9 +2537,9 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.6">
-      <c r="A57" s="67"/>
+      <c r="A57" s="70"/>
       <c r="B57" s="39" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C57" s="52">
         <f>'云相册-城市统计'!B6</f>
@@ -2538,9 +2558,9 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.6">
-      <c r="A58" s="67"/>
+      <c r="A58" s="70"/>
       <c r="B58" s="39" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C58" s="52">
         <f>'云相册-城市统计'!B7</f>
@@ -2559,9 +2579,9 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.6">
-      <c r="A59" s="67"/>
+      <c r="A59" s="70"/>
       <c r="B59" s="39" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C59" s="52">
         <f>'云相册-城市统计'!B8</f>
@@ -2580,9 +2600,9 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.6">
-      <c r="A60" s="67"/>
+      <c r="A60" s="70"/>
       <c r="B60" s="39" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C60" s="52">
         <f>'云相册-城市统计'!B9</f>
@@ -2601,9 +2621,9 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.6">
-      <c r="A61" s="67"/>
+      <c r="A61" s="70"/>
       <c r="B61" s="39" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C61" s="52">
         <f>'云相册-城市统计'!B10</f>
@@ -2622,9 +2642,9 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.6">
-      <c r="A62" s="68"/>
+      <c r="A62" s="71"/>
       <c r="B62" s="39" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C62" s="52">
         <f>'云相册-城市统计'!B11</f>
@@ -2644,17 +2664,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A53:A62"/>
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="A48:A52"/>
     <mergeCell ref="A2:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="A48:A52"/>
-    <mergeCell ref="A53:A62"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2672,34 +2692,34 @@
   <sheetData>
     <row r="1" spans="1:2" ht="95.4" customHeight="1">
       <c r="A1" s="55" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B1" s="56" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="57" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="57" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="57" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2723,27 +2743,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="73" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="74"/>
+      <c r="A1" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="76"/>
       <c r="E1" s="18"/>
       <c r="F1" s="19" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="85" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="86"/>
+      <c r="A2" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="78"/>
       <c r="C2" s="20" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="18"/>
@@ -2755,14 +2775,14 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="87" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="78" t="s">
-        <v>83</v>
+      <c r="A3" s="79" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="82" t="s">
+        <v>77</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D3" s="23">
         <v>10901</v>
@@ -2772,10 +2792,10 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="88"/>
-      <c r="B4" s="80"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="23" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D4" s="23">
         <v>1537</v>
@@ -2785,12 +2805,12 @@
       <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="88"/>
-      <c r="B5" s="78" t="s">
-        <v>85</v>
+      <c r="A5" s="80"/>
+      <c r="B5" s="82" t="s">
+        <v>79</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D5" s="23">
         <v>602820</v>
@@ -2800,10 +2820,10 @@
       <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="88"/>
-      <c r="B6" s="80"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="83"/>
       <c r="C6" s="24" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D6" s="24">
         <v>1777</v>
@@ -2813,12 +2833,12 @@
       <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90" t="s">
-        <v>88</v>
+      <c r="A7" s="80"/>
+      <c r="B7" s="84" t="s">
+        <v>82</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D7" s="26">
         <v>441</v>
@@ -2828,10 +2848,10 @@
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="88"/>
-      <c r="B8" s="91"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="85"/>
       <c r="C8" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D8" s="27">
         <v>31</v>
@@ -2841,10 +2861,10 @@
       <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="88"/>
-      <c r="B9" s="91"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="85"/>
       <c r="C9" s="25" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D9" s="25">
         <v>14</v>
@@ -2854,10 +2874,10 @@
       <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="88"/>
-      <c r="B10" s="92"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="86"/>
       <c r="C10" s="25" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D10" s="25">
         <v>7</v>
@@ -2867,12 +2887,12 @@
       <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90" t="s">
-        <v>93</v>
+      <c r="A11" s="80"/>
+      <c r="B11" s="84" t="s">
+        <v>87</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D11" s="25">
         <v>468</v>
@@ -2882,10 +2902,10 @@
       <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="25" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D12" s="25">
         <v>186</v>
@@ -2895,10 +2915,10 @@
       <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="88"/>
-      <c r="B13" s="91"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="25" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D13" s="25">
         <v>89</v>
@@ -2908,10 +2928,10 @@
       <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="80"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="25" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D14" s="25">
         <v>380</v>
@@ -2921,25 +2941,25 @@
       <c r="G14" s="18"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="88"/>
-      <c r="B15" s="78" t="s">
-        <v>98</v>
+      <c r="A15" s="80"/>
+      <c r="B15" s="82" t="s">
+        <v>92</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="88"/>
-      <c r="B16" s="79"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="87"/>
       <c r="C16" s="23" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D16" s="23">
         <v>1335</v>
@@ -2949,10 +2969,10 @@
       <c r="G16" s="18"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="88"/>
-      <c r="B17" s="79"/>
+      <c r="A17" s="80"/>
+      <c r="B17" s="87"/>
       <c r="C17" s="23" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D17" s="23">
         <v>4</v>
@@ -2962,10 +2982,10 @@
       <c r="G17" s="18"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="88"/>
-      <c r="B18" s="79"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="87"/>
       <c r="C18" s="23" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D18" s="23">
         <v>325</v>
@@ -2975,10 +2995,10 @@
       <c r="G18" s="18"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="89"/>
-      <c r="B19" s="80"/>
+      <c r="A19" s="81"/>
+      <c r="B19" s="83"/>
       <c r="C19" s="28" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D19" s="28">
         <v>9</v>
@@ -2988,14 +3008,14 @@
       <c r="G19" s="18"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="75" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="78" t="s">
-        <v>106</v>
+      <c r="A20" s="88" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="82" t="s">
+        <v>100</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D20" s="23">
         <v>8816</v>
@@ -3005,10 +3025,10 @@
       <c r="G20" s="18"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="76"/>
-      <c r="B21" s="79"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="87"/>
       <c r="C21" s="20" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D21" s="23">
         <v>3615</v>
@@ -3018,10 +3038,10 @@
       <c r="G21" s="18"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="76"/>
-      <c r="B22" s="79"/>
+      <c r="A22" s="89"/>
+      <c r="B22" s="87"/>
       <c r="C22" s="23" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D22" s="23">
         <v>22</v>
@@ -3031,10 +3051,10 @@
       <c r="G22" s="18"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="76"/>
-      <c r="B23" s="79"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="87"/>
       <c r="C23" s="23" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D23" s="23">
         <v>836</v>
@@ -3044,10 +3064,10 @@
       <c r="G23" s="18"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="76"/>
-      <c r="B24" s="79"/>
+      <c r="A24" s="89"/>
+      <c r="B24" s="87"/>
       <c r="C24" s="23" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D24" s="23">
         <v>2165</v>
@@ -3057,10 +3077,10 @@
       <c r="G24" s="18"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="76"/>
-      <c r="B25" s="79"/>
+      <c r="A25" s="89"/>
+      <c r="B25" s="87"/>
       <c r="C25" s="23" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D25" s="23">
         <v>1079</v>
@@ -3070,51 +3090,51 @@
       <c r="G25" s="18"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="76"/>
-      <c r="B26" s="79"/>
+      <c r="A26" s="89"/>
+      <c r="B26" s="87"/>
       <c r="C26" s="23" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="76"/>
-      <c r="B27" s="79"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="87"/>
       <c r="C27" s="23" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="76"/>
-      <c r="B28" s="80"/>
+      <c r="A28" s="89"/>
+      <c r="B28" s="83"/>
       <c r="C28" s="23" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="76"/>
-      <c r="B29" s="81" t="s">
-        <v>115</v>
+      <c r="A29" s="89"/>
+      <c r="B29" s="91" t="s">
+        <v>109</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D29" s="29">
         <v>13036</v>
@@ -3124,25 +3144,25 @@
       <c r="G29" s="18"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="76"/>
-      <c r="B30" s="82"/>
+      <c r="A30" s="89"/>
+      <c r="B30" s="92"/>
       <c r="C30" s="30" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="76"/>
-      <c r="B31" s="81" t="s">
-        <v>118</v>
+      <c r="A31" s="89"/>
+      <c r="B31" s="91" t="s">
+        <v>112</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D31" s="32">
         <v>1465</v>
@@ -3152,27 +3172,27 @@
       <c r="G31" s="18"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="76"/>
-      <c r="B32" s="83"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="93"/>
       <c r="C32" s="32" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D32" s="32">
         <v>6846</v>
       </c>
       <c r="E32" s="18"/>
       <c r="F32" s="33" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G32" s="25">
         <v>6801</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="76"/>
-      <c r="B33" s="83"/>
+      <c r="A33" s="89"/>
+      <c r="B33" s="93"/>
       <c r="C33" s="32" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D33" s="32">
         <v>190</v>
@@ -3182,30 +3202,30 @@
       <c r="G33" s="17"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="77"/>
-      <c r="B34" s="82"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="92"/>
       <c r="C34" s="32" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D34" s="32">
         <v>288</v>
       </c>
       <c r="E34" s="18"/>
       <c r="F34" s="33" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G34" s="25">
         <v>283</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="75" t="s">
-        <v>124</v>
-      </c>
-      <c r="B35" s="73" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="74"/>
+      <c r="A35" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="76"/>
       <c r="D35" s="25">
         <v>321</v>
       </c>
@@ -3216,11 +3236,11 @@
       <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="76"/>
-      <c r="B36" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="74"/>
+      <c r="A36" s="89"/>
+      <c r="B36" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="76"/>
       <c r="D36" s="25">
         <v>87707</v>
       </c>
@@ -3231,11 +3251,11 @@
       <c r="G36" s="18"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="76"/>
-      <c r="B37" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="74"/>
+      <c r="A37" s="89"/>
+      <c r="B37" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="76"/>
       <c r="D37" s="25">
         <v>63519.1</v>
       </c>
@@ -3246,11 +3266,11 @@
       <c r="G37" s="18"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="76"/>
-      <c r="B38" s="73" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="74"/>
+      <c r="A38" s="89"/>
+      <c r="B38" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="76"/>
       <c r="D38" s="25">
         <v>36170.99</v>
       </c>
@@ -3261,11 +3281,11 @@
       <c r="G38" s="18"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="76"/>
-      <c r="B39" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="74"/>
+      <c r="A39" s="89"/>
+      <c r="B39" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="76"/>
       <c r="D39" s="25">
         <v>27348.11</v>
       </c>
@@ -3276,11 +3296,11 @@
       <c r="G39" s="18"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="77"/>
-      <c r="B40" s="73" t="s">
-        <v>125</v>
-      </c>
-      <c r="C40" s="74"/>
+      <c r="A40" s="90"/>
+      <c r="B40" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="76"/>
       <c r="D40" s="25">
         <v>11156</v>
       </c>
@@ -3292,14 +3312,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:A19"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="B15:B19"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="A20:A34"/>
     <mergeCell ref="B20:B28"/>
@@ -3311,6 +3323,14 @@
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:A19"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="B15:B19"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3385,7 +3405,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="42" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B8" s="45">
         <f>AVERAGE(B1:B7)</f>
@@ -3393,16 +3413,16 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="93" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="93" t="s">
-        <v>128</v>
+      <c r="A10" s="94" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="94" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="93"/>
-      <c r="B11" s="93"/>
+      <c r="A11" s="94"/>
+      <c r="B11" s="94"/>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="47">
@@ -3433,15 +3453,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="50" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4">
       <c r="A2" s="51" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B2" s="51">
         <v>315</v>
@@ -3449,7 +3469,7 @@
     </row>
     <row r="3" spans="1:2" ht="14.4">
       <c r="A3" s="51" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B3" s="51">
         <v>86</v>
@@ -3457,7 +3477,7 @@
     </row>
     <row r="4" spans="1:2" ht="14.4">
       <c r="A4" s="51" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B4" s="51">
         <v>55</v>
@@ -3465,7 +3485,7 @@
     </row>
     <row r="5" spans="1:2" ht="14.4">
       <c r="A5" s="51" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B5" s="51">
         <v>49</v>
@@ -3473,7 +3493,7 @@
     </row>
     <row r="6" spans="1:2" ht="14.4">
       <c r="A6" s="51" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B6" s="51">
         <v>46</v>
@@ -3481,7 +3501,7 @@
     </row>
     <row r="7" spans="1:2" ht="14.4">
       <c r="A7" s="51" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B7" s="51">
         <v>45</v>
@@ -3489,7 +3509,7 @@
     </row>
     <row r="8" spans="1:2" ht="14.4">
       <c r="A8" s="51" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B8" s="51">
         <v>35</v>
@@ -3497,7 +3517,7 @@
     </row>
     <row r="9" spans="1:2" ht="14.4">
       <c r="A9" s="51" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B9" s="51">
         <v>33</v>
@@ -3505,7 +3525,7 @@
     </row>
     <row r="10" spans="1:2" ht="14.4">
       <c r="A10" s="51" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B10" s="51">
         <v>33</v>
@@ -3513,7 +3533,7 @@
     </row>
     <row r="11" spans="1:2" ht="14.4">
       <c r="A11" s="51" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B11" s="51">
         <v>32</v>

--- a/业务数据统计模板.xlsx
+++ b/业务数据统计模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WasuProject\GitHub\DataStatistic\DataStatistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EC9236-7B84-40AB-9BB2-229A8951E479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559BA498-86D8-419E-B42C-D2CDFEC59028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
   <si>
     <t>业务模块</t>
   </si>
@@ -543,6 +543,22 @@
   </si>
   <si>
     <t>7天全时段连续包月（线下）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>30天全时段连续包月（线下）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>3天全时段连续包月（线下）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>3天事件连续包月（线下）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>政企云存（线下）</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -948,7 +964,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1131,6 +1147,18 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1143,25 +1171,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1179,12 +1222,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1194,30 +1231,11 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1493,7 +1511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13.77734375" customWidth="1"/>
@@ -1525,7 +1543,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.2">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="37" t="s">
@@ -1540,13 +1558,13 @@
         <v>59014</v>
       </c>
       <c r="E2" s="6">
-        <f t="shared" ref="E2:E43" si="0">(C2-D2)/D2</f>
+        <f t="shared" ref="E2:E47" si="0">(C2-D2)/D2</f>
         <v>6.1138035042532284E-2</v>
       </c>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="16.2">
-      <c r="A3" s="65"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1563,7 +1581,7 @@
       <c r="F3" s="59"/>
     </row>
     <row r="4" spans="1:6" ht="16.2">
-      <c r="A4" s="65"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1580,7 +1598,7 @@
       <c r="F4" s="60"/>
     </row>
     <row r="5" spans="1:6" ht="16.2">
-      <c r="A5" s="65"/>
+      <c r="A5" s="71"/>
       <c r="B5" s="37" t="s">
         <v>10</v>
       </c>
@@ -1599,7 +1617,7 @@
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="16.2">
-      <c r="A6" s="65"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="37" t="s">
         <v>11</v>
       </c>
@@ -1617,7 +1635,7 @@
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" ht="16.2">
-      <c r="A7" s="65"/>
+      <c r="A7" s="71"/>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1634,7 +1652,7 @@
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" ht="16.2">
-      <c r="A8" s="65"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="61" t="s">
         <v>131</v>
       </c>
@@ -1651,7 +1669,7 @@
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" ht="16.2">
-      <c r="A9" s="66"/>
+      <c r="A9" s="72"/>
       <c r="B9" s="61" t="s">
         <v>132</v>
       </c>
@@ -1668,7 +1686,7 @@
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="73" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="39" t="s">
@@ -1688,7 +1706,7 @@
       <c r="F10" s="58"/>
     </row>
     <row r="11" spans="1:6" ht="15">
-      <c r="A11" s="67"/>
+      <c r="A11" s="73"/>
       <c r="B11" s="39" t="s">
         <v>15</v>
       </c>
@@ -1706,7 +1724,7 @@
       <c r="F11" s="58"/>
     </row>
     <row r="12" spans="1:6" ht="15">
-      <c r="A12" s="67"/>
+      <c r="A12" s="73"/>
       <c r="B12" s="48" t="s">
         <v>16</v>
       </c>
@@ -1724,7 +1742,7 @@
       <c r="F12" s="58"/>
     </row>
     <row r="13" spans="1:6" ht="30">
-      <c r="A13" s="66"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="48" t="s">
         <v>17</v>
       </c>
@@ -1905,7 +1923,7 @@
       <c r="F22" s="58"/>
     </row>
     <row r="23" spans="1:6" ht="30">
-      <c r="A23" s="69" t="s">
+      <c r="A23" s="67" t="s">
         <v>135</v>
       </c>
       <c r="B23" s="63" t="s">
@@ -1925,7 +1943,7 @@
       <c r="F23" s="58"/>
     </row>
     <row r="24" spans="1:6" ht="30">
-      <c r="A24" s="70"/>
+      <c r="A24" s="65"/>
       <c r="B24" s="63" t="s">
         <v>139</v>
       </c>
@@ -1943,7 +1961,7 @@
       <c r="F24" s="58"/>
     </row>
     <row r="25" spans="1:6" ht="30">
-      <c r="A25" s="70"/>
+      <c r="A25" s="65"/>
       <c r="B25" s="63" t="s">
         <v>140</v>
       </c>
@@ -1961,7 +1979,7 @@
       <c r="F25" s="58"/>
     </row>
     <row r="26" spans="1:6" ht="30">
-      <c r="A26" s="71"/>
+      <c r="A26" s="66"/>
       <c r="B26" s="63" t="s">
         <v>141</v>
       </c>
@@ -1979,7 +1997,7 @@
       <c r="F26" s="58"/>
     </row>
     <row r="27" spans="1:6" ht="30">
-      <c r="A27" s="69" t="s">
+      <c r="A27" s="67" t="s">
         <v>136</v>
       </c>
       <c r="B27" s="63" t="s">
@@ -1999,7 +2017,7 @@
       <c r="F27" s="58"/>
     </row>
     <row r="28" spans="1:6" ht="30">
-      <c r="A28" s="70"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="63" t="s">
         <v>142</v>
       </c>
@@ -2017,7 +2035,7 @@
       <c r="F28" s="58"/>
     </row>
     <row r="29" spans="1:6" ht="30">
-      <c r="A29" s="70"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="63" t="s">
         <v>143</v>
       </c>
@@ -2035,7 +2053,7 @@
       <c r="F29" s="58"/>
     </row>
     <row r="30" spans="1:6" ht="30">
-      <c r="A30" s="70"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="63" t="s">
         <v>144</v>
       </c>
@@ -2053,7 +2071,7 @@
       <c r="F30" s="58"/>
     </row>
     <row r="31" spans="1:6" ht="30">
-      <c r="A31" s="70"/>
+      <c r="A31" s="95"/>
       <c r="B31" s="63" t="s">
         <v>145</v>
       </c>
@@ -2071,7 +2089,7 @@
       <c r="F31" s="58"/>
     </row>
     <row r="32" spans="1:6" ht="30">
-      <c r="A32" s="71"/>
+      <c r="A32" s="95"/>
       <c r="B32" s="63" t="s">
         <v>146</v>
       </c>
@@ -2088,596 +2106,669 @@
       </c>
       <c r="F32" s="58"/>
     </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1">
-      <c r="A33" s="68" t="s">
+    <row r="33" spans="1:7" ht="30">
+      <c r="A33" s="95"/>
+      <c r="B33" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="39">
+        <f>业务数据统计!G34</f>
+        <v>283</v>
+      </c>
+      <c r="D33" s="8">
+        <v>281</v>
+      </c>
+      <c r="E33" s="9">
+        <f t="shared" ref="E33" si="2">(C33-D33)/D33</f>
+        <v>7.1174377224199285E-3</v>
+      </c>
+      <c r="F33" s="58"/>
+    </row>
+    <row r="34" spans="1:7" ht="30">
+      <c r="A34" s="95"/>
+      <c r="B34" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="39">
+        <f>业务数据统计!G34</f>
+        <v>283</v>
+      </c>
+      <c r="D34" s="8">
+        <v>281</v>
+      </c>
+      <c r="E34" s="9">
+        <f t="shared" ref="E34:E36" si="3">(C34-D34)/D34</f>
+        <v>7.1174377224199285E-3</v>
+      </c>
+      <c r="F34" s="58"/>
+    </row>
+    <row r="35" spans="1:7" ht="30">
+      <c r="A35" s="95"/>
+      <c r="B35" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="39">
+        <f>业务数据统计!G34</f>
+        <v>283</v>
+      </c>
+      <c r="D35" s="8">
+        <v>281</v>
+      </c>
+      <c r="E35" s="9">
+        <f t="shared" si="3"/>
+        <v>7.1174377224199285E-3</v>
+      </c>
+      <c r="F35" s="58"/>
+    </row>
+    <row r="36" spans="1:7" ht="15">
+      <c r="A36" s="96"/>
+      <c r="B36" s="63" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="39">
+        <f>业务数据统计!G34</f>
+        <v>283</v>
+      </c>
+      <c r="D36" s="8">
+        <v>281</v>
+      </c>
+      <c r="E36" s="9">
+        <f t="shared" si="3"/>
+        <v>7.1174377224199285E-3</v>
+      </c>
+      <c r="F36" s="58"/>
+    </row>
+    <row r="37" spans="1:7" ht="15" customHeight="1">
+      <c r="A37" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="39" t="s">
+      <c r="B37" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="39">
+      <c r="C37" s="39">
         <f>5859+C20</f>
         <v>6953</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D37" s="8">
         <f>5521+994</f>
         <v>6515</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E37" s="9">
         <f t="shared" si="0"/>
         <v>6.7229470452801227E-2</v>
       </c>
-      <c r="F33" s="58"/>
-    </row>
-    <row r="34" spans="1:7" ht="15">
-      <c r="A34" s="72"/>
-      <c r="B34" s="8" t="s">
+      <c r="F37" s="58"/>
+    </row>
+    <row r="38" spans="1:7" ht="15">
+      <c r="A38" s="69"/>
+      <c r="B38" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C38" s="12">
         <v>0.46300000000000002</v>
       </c>
-      <c r="D34" s="12">
-        <f>D33/14514</f>
+      <c r="D38" s="12">
+        <f>D37/14514</f>
         <v>0.4488769463965826</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E38" s="13">
         <f t="shared" si="0"/>
         <v>3.1463085188027706E-2</v>
       </c>
-      <c r="F34" s="58"/>
-    </row>
-    <row r="35" spans="1:7" ht="15">
-      <c r="A35" s="72"/>
-      <c r="B35" s="61" t="s">
+      <c r="F38" s="58"/>
+    </row>
+    <row r="39" spans="1:7" ht="15">
+      <c r="A39" s="69"/>
+      <c r="B39" s="61" t="s">
         <v>133</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C39" s="8">
         <v>1963</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D39" s="8">
         <v>2114</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E39" s="9">
         <f t="shared" si="0"/>
         <v>-7.1428571428571425E-2</v>
       </c>
-      <c r="F35" s="58"/>
-    </row>
-    <row r="36" spans="1:7" ht="15">
-      <c r="A36" s="72"/>
-      <c r="B36" s="39" t="s">
+      <c r="F39" s="58"/>
+    </row>
+    <row r="40" spans="1:7" ht="15">
+      <c r="A40" s="69"/>
+      <c r="B40" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C40" s="39">
         <f>业务数据统计!D21</f>
         <v>3615</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D40" s="8">
         <v>3400</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E40" s="9">
         <f t="shared" si="0"/>
         <v>6.3235294117647056E-2</v>
       </c>
-      <c r="F36" s="58"/>
-    </row>
-    <row r="37" spans="1:7" ht="15">
-      <c r="A37" s="72"/>
-      <c r="B37" s="39" t="s">
+      <c r="F40" s="58"/>
+    </row>
+    <row r="41" spans="1:7" ht="15">
+      <c r="A41" s="69"/>
+      <c r="B41" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="40">
+      <c r="C41" s="40">
         <f>C19/C17</f>
         <v>0.49748978897208984</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D41" s="12">
         <f>D19/D17</f>
         <v>0.48975113022867928</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E41" s="9">
         <f t="shared" si="0"/>
         <v>1.5801206502161939E-2</v>
       </c>
-      <c r="F37" s="58"/>
-    </row>
-    <row r="38" spans="1:7" ht="15">
-      <c r="A38" s="72"/>
-      <c r="B38" s="39" t="s">
+      <c r="F41" s="58"/>
+    </row>
+    <row r="42" spans="1:7" ht="15">
+      <c r="A42" s="69"/>
+      <c r="B42" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="40">
+      <c r="C42" s="40">
         <f>业务数据统计!D20/主表!C19</f>
         <v>0.75395535790643975</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D42" s="12">
         <f>8215/D19</f>
         <v>0.73624305431080839</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E42" s="13">
         <f t="shared" si="0"/>
         <v>2.4057685151558702E-2</v>
       </c>
-      <c r="F38" s="58"/>
-    </row>
-    <row r="39" spans="1:7" ht="15">
-      <c r="A39" s="68" t="s">
+      <c r="F42" s="58"/>
+    </row>
+    <row r="43" spans="1:7" ht="15">
+      <c r="A43" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B43" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="39">
+      <c r="C43" s="39">
         <f>业务数据统计!D3</f>
         <v>10901</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D43" s="14">
         <v>7295</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E43" s="9">
         <f t="shared" si="0"/>
         <v>0.49431117203564084</v>
       </c>
-      <c r="F39" s="58"/>
-    </row>
-    <row r="40" spans="1:7" ht="15">
-      <c r="A40" s="72"/>
-      <c r="B40" s="39" t="s">
+      <c r="F43" s="58"/>
+    </row>
+    <row r="44" spans="1:7" ht="15">
+      <c r="A44" s="69"/>
+      <c r="B44" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="39">
+      <c r="C44" s="39">
         <f>业务数据统计!D4</f>
         <v>1537</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D44" s="14">
         <v>1458</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E44" s="9">
         <f t="shared" si="0"/>
         <v>5.4183813443072701E-2</v>
       </c>
-      <c r="F40" s="58"/>
-    </row>
-    <row r="41" spans="1:7" ht="15">
-      <c r="A41" s="72"/>
-      <c r="B41" s="39" t="s">
+      <c r="F44" s="58"/>
+    </row>
+    <row r="45" spans="1:7" ht="15">
+      <c r="A45" s="69"/>
+      <c r="B45" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="C41" s="39">
+      <c r="C45" s="39">
         <f>业务数据统计!D5</f>
         <v>602820</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D45" s="14">
         <v>121740</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E45" s="9">
         <f t="shared" si="0"/>
         <v>3.9517003449975356</v>
       </c>
-      <c r="F41" s="58"/>
-    </row>
-    <row r="42" spans="1:7" ht="15">
-      <c r="A42" s="72"/>
-      <c r="B42" s="39" t="s">
+      <c r="F45" s="58"/>
+    </row>
+    <row r="46" spans="1:7" ht="15">
+      <c r="A46" s="69"/>
+      <c r="B46" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="39">
+      <c r="C46" s="39">
         <f>业务数据统计!D6</f>
         <v>1777</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D46" s="14">
         <v>1735</v>
       </c>
-      <c r="E42" s="9">
-        <f t="shared" ref="E42" si="2">(C42-D42)/D42</f>
+      <c r="E46" s="9">
+        <f t="shared" ref="E46" si="4">(C46-D46)/D46</f>
         <v>2.420749279538905E-2</v>
       </c>
-      <c r="F42" s="58"/>
-      <c r="G42" s="62"/>
-    </row>
-    <row r="43" spans="1:7" ht="15">
-      <c r="A43" s="72"/>
-      <c r="B43" s="63" t="s">
+      <c r="F46" s="58"/>
+      <c r="G46" s="62"/>
+    </row>
+    <row r="47" spans="1:7" ht="15">
+      <c r="A47" s="69"/>
+      <c r="B47" s="63" t="s">
         <v>134</v>
       </c>
-      <c r="C43" s="39">
+      <c r="C47" s="39">
         <v>1856</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D47" s="14">
         <v>1735</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E47" s="9">
         <f t="shared" si="0"/>
         <v>6.9740634005763691E-2</v>
       </c>
-      <c r="F43" s="58"/>
-    </row>
-    <row r="44" spans="1:7" ht="15">
-      <c r="A44" s="68" t="s">
+      <c r="F47" s="58"/>
+    </row>
+    <row r="48" spans="1:7" ht="15">
+      <c r="A48" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="39" t="s">
+      <c r="B48" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="39">
+      <c r="C48" s="39">
         <f>业务数据统计!D16</f>
         <v>1335</v>
       </c>
-      <c r="D44" s="12">
-        <f>C44/C40</f>
+      <c r="D48" s="12">
+        <f>C48/C44</f>
         <v>0.86857514638906963</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="58"/>
-    </row>
-    <row r="45" spans="1:7" ht="15">
-      <c r="A45" s="72"/>
-      <c r="B45" s="39" t="s">
+      <c r="E48" s="9"/>
+      <c r="F48" s="58"/>
+    </row>
+    <row r="49" spans="1:6" ht="15">
+      <c r="A49" s="69"/>
+      <c r="B49" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="39">
+      <c r="C49" s="39">
         <f>业务数据统计!D18</f>
         <v>325</v>
       </c>
-      <c r="D45" s="12">
-        <f>C45/C40</f>
+      <c r="D49" s="12">
+        <f>C49/C44</f>
         <v>0.2114508783344177</v>
       </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="58"/>
-    </row>
-    <row r="46" spans="1:7" ht="15">
-      <c r="A46" s="72"/>
-      <c r="B46" s="39" t="s">
+      <c r="E49" s="9"/>
+      <c r="F49" s="58"/>
+    </row>
+    <row r="50" spans="1:6" ht="15">
+      <c r="A50" s="69"/>
+      <c r="B50" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C46" s="39">
+      <c r="C50" s="39">
         <f>业务数据统计!D17</f>
         <v>4</v>
       </c>
-      <c r="D46" s="12">
-        <f>C46/C40</f>
+      <c r="D50" s="12">
+        <f>C50/C44</f>
         <v>2.6024723487312949E-3</v>
       </c>
-      <c r="E46" s="9"/>
-      <c r="F46" s="58"/>
-    </row>
-    <row r="47" spans="1:7" ht="15">
-      <c r="A47" s="72"/>
-      <c r="B47" s="39" t="s">
+      <c r="E50" s="9"/>
+      <c r="F50" s="58"/>
+    </row>
+    <row r="51" spans="1:6" ht="15">
+      <c r="A51" s="69"/>
+      <c r="B51" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="39">
+      <c r="C51" s="39">
         <f>业务数据统计!D19</f>
         <v>9</v>
       </c>
-      <c r="D47" s="12">
-        <f>C47/C40</f>
+      <c r="D51" s="12">
+        <f>C51/C44</f>
         <v>5.8555627846454128E-3</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="58"/>
-    </row>
-    <row r="48" spans="1:7" ht="15">
-      <c r="A48" s="68" t="s">
+      <c r="E51" s="9"/>
+      <c r="F51" s="58"/>
+    </row>
+    <row r="52" spans="1:6" ht="15">
+      <c r="A52" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="39" t="s">
+      <c r="B52" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="C48" s="41">
+      <c r="C52" s="41">
         <f>业务数据统计!D35</f>
         <v>321</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D52" s="14">
         <v>321</v>
       </c>
-      <c r="E48" s="9">
-        <f t="shared" ref="E48:E62" si="3">(C48-D48)/D48</f>
+      <c r="E52" s="9">
+        <f t="shared" ref="E52:E66" si="5">(C52-D52)/D52</f>
         <v>0</v>
       </c>
-      <c r="F48" s="58"/>
-    </row>
-    <row r="49" spans="1:6" ht="15">
-      <c r="A49" s="72"/>
-      <c r="B49" s="39" t="s">
+      <c r="F52" s="58"/>
+    </row>
+    <row r="53" spans="1:6" ht="15">
+      <c r="A53" s="69"/>
+      <c r="B53" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="C49" s="41">
+      <c r="C53" s="41">
         <f>业务数据统计!D36</f>
         <v>87707</v>
       </c>
-      <c r="D49" s="14">
+      <c r="D53" s="14">
         <v>79012</v>
       </c>
-      <c r="E49" s="9">
-        <f t="shared" si="3"/>
+      <c r="E53" s="9">
+        <f t="shared" si="5"/>
         <v>0.11004657520376651</v>
       </c>
-      <c r="F49" s="58"/>
-    </row>
-    <row r="50" spans="1:6" ht="15">
-      <c r="A50" s="72"/>
-      <c r="B50" s="39" t="s">
+      <c r="F53" s="58"/>
+    </row>
+    <row r="54" spans="1:6" ht="15">
+      <c r="A54" s="69"/>
+      <c r="B54" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="41">
+      <c r="C54" s="41">
         <f>业务数据统计!D37</f>
         <v>63519.1</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D54" s="14">
         <v>57685.66</v>
       </c>
-      <c r="E50" s="9">
-        <f t="shared" si="3"/>
+      <c r="E54" s="9">
+        <f t="shared" si="5"/>
         <v>0.10112461225198767</v>
       </c>
-      <c r="F50" s="58"/>
-    </row>
-    <row r="51" spans="1:6" ht="15">
-      <c r="A51" s="72"/>
-      <c r="B51" s="39" t="s">
+      <c r="F54" s="58"/>
+    </row>
+    <row r="55" spans="1:6" ht="15">
+      <c r="A55" s="69"/>
+      <c r="B55" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="41">
+      <c r="C55" s="41">
         <f>业务数据统计!D38</f>
         <v>36170.99</v>
       </c>
-      <c r="D51" s="14">
+      <c r="D55" s="14">
         <v>32900.660000000003</v>
       </c>
-      <c r="E51" s="9">
-        <f t="shared" si="3"/>
+      <c r="E55" s="9">
+        <f t="shared" si="5"/>
         <v>9.9400133614340691E-2</v>
       </c>
-      <c r="F51" s="58"/>
-    </row>
-    <row r="52" spans="1:6" ht="15">
-      <c r="A52" s="72"/>
-      <c r="B52" s="39" t="s">
+      <c r="F55" s="58"/>
+    </row>
+    <row r="56" spans="1:6" ht="15">
+      <c r="A56" s="69"/>
+      <c r="B56" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="C52" s="41">
+      <c r="C56" s="41">
         <f>业务数据统计!D39</f>
         <v>27348.11</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D56" s="14">
         <v>24785</v>
       </c>
-      <c r="E52" s="9">
-        <f t="shared" si="3"/>
+      <c r="E56" s="9">
+        <f t="shared" si="5"/>
         <v>0.10341375832156549</v>
       </c>
-      <c r="F52" s="58"/>
-    </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1">
-      <c r="A53" s="73" t="s">
+      <c r="F56" s="58"/>
+    </row>
+    <row r="57" spans="1:6" ht="15" customHeight="1">
+      <c r="A57" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="39" t="s">
+      <c r="B57" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="52">
+      <c r="C57" s="52">
         <f>'云相册-城市统计'!B2</f>
         <v>315</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D57" s="15">
         <v>301</v>
       </c>
-      <c r="E53" s="9">
-        <f t="shared" si="3"/>
+      <c r="E57" s="9">
+        <f t="shared" si="5"/>
         <v>4.6511627906976744E-2</v>
       </c>
-      <c r="F53" s="53" t="str">
+      <c r="F57" s="53" t="str">
         <f>'云相册-城市统计'!A2</f>
         <v>杭州市</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.6">
-      <c r="A54" s="70"/>
-      <c r="B54" s="39" t="s">
+    <row r="58" spans="1:6" ht="15.6">
+      <c r="A58" s="65"/>
+      <c r="B58" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="52">
+      <c r="C58" s="52">
         <f>'云相册-城市统计'!B3</f>
         <v>86</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D58" s="16">
         <v>75</v>
       </c>
-      <c r="E54" s="9">
-        <f t="shared" si="3"/>
+      <c r="E58" s="9">
+        <f t="shared" si="5"/>
         <v>0.14666666666666667</v>
       </c>
-      <c r="F54" s="53" t="str">
+      <c r="F58" s="53" t="str">
         <f>'云相册-城市统计'!A3</f>
         <v>金华市</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.6">
-      <c r="A55" s="70"/>
-      <c r="B55" s="39" t="s">
+    <row r="59" spans="1:6" ht="15.6">
+      <c r="A59" s="65"/>
+      <c r="B59" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="52">
+      <c r="C59" s="52">
         <f>'云相册-城市统计'!B4</f>
         <v>55</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D59" s="16">
         <v>54</v>
       </c>
-      <c r="E55" s="9">
-        <f t="shared" si="3"/>
+      <c r="E59" s="9">
+        <f t="shared" si="5"/>
         <v>1.8518518518518517E-2</v>
       </c>
-      <c r="F55" s="53" t="str">
+      <c r="F59" s="53" t="str">
         <f>'云相册-城市统计'!A4</f>
         <v>绍兴市</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.6">
-      <c r="A56" s="70"/>
-      <c r="B56" s="39" t="s">
+    <row r="60" spans="1:6" ht="15.6">
+      <c r="A60" s="65"/>
+      <c r="B60" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C56" s="52">
+      <c r="C60" s="52">
         <f>'云相册-城市统计'!B5</f>
         <v>49</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D60" s="16">
         <v>46</v>
       </c>
-      <c r="E56" s="9">
-        <f t="shared" si="3"/>
+      <c r="E60" s="9">
+        <f t="shared" si="5"/>
         <v>6.5217391304347824E-2</v>
       </c>
-      <c r="F56" s="53" t="str">
+      <c r="F60" s="53" t="str">
         <f>'云相册-城市统计'!A5</f>
         <v>湖州市</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.6">
-      <c r="A57" s="70"/>
-      <c r="B57" s="39" t="s">
+    <row r="61" spans="1:6" ht="15.6">
+      <c r="A61" s="65"/>
+      <c r="B61" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C57" s="52">
+      <c r="C61" s="52">
         <f>'云相册-城市统计'!B6</f>
         <v>46</v>
       </c>
-      <c r="D57" s="16">
+      <c r="D61" s="16">
         <v>40</v>
       </c>
-      <c r="E57" s="9">
-        <f t="shared" si="3"/>
+      <c r="E61" s="9">
+        <f t="shared" si="5"/>
         <v>0.15</v>
       </c>
-      <c r="F57" s="53" t="str">
+      <c r="F61" s="53" t="str">
         <f>'云相册-城市统计'!A6</f>
         <v>衢州市</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.6">
-      <c r="A58" s="70"/>
-      <c r="B58" s="39" t="s">
+    <row r="62" spans="1:6" ht="15.6">
+      <c r="A62" s="65"/>
+      <c r="B62" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="C58" s="52">
+      <c r="C62" s="52">
         <f>'云相册-城市统计'!B7</f>
         <v>45</v>
       </c>
-      <c r="D58" s="16">
+      <c r="D62" s="16">
         <v>43</v>
       </c>
-      <c r="E58" s="9">
-        <f t="shared" si="3"/>
+      <c r="E62" s="9">
+        <f t="shared" si="5"/>
         <v>4.6511627906976744E-2</v>
       </c>
-      <c r="F58" s="53" t="str">
+      <c r="F62" s="53" t="str">
         <f>'云相册-城市统计'!A7</f>
         <v>嘉兴市</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.6">
-      <c r="A59" s="70"/>
-      <c r="B59" s="39" t="s">
+    <row r="63" spans="1:6" ht="15.6">
+      <c r="A63" s="65"/>
+      <c r="B63" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="52">
+      <c r="C63" s="52">
         <f>'云相册-城市统计'!B8</f>
         <v>35</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D63" s="16">
         <v>35</v>
       </c>
-      <c r="E59" s="9">
-        <f t="shared" si="3"/>
+      <c r="E63" s="9">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F59" s="53" t="str">
+      <c r="F63" s="53" t="str">
         <f>'云相册-城市统计'!A8</f>
         <v>上海市</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.6">
-      <c r="A60" s="70"/>
-      <c r="B60" s="39" t="s">
+    <row r="64" spans="1:6" ht="15.6">
+      <c r="A64" s="65"/>
+      <c r="B64" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="C60" s="52">
+      <c r="C64" s="52">
         <f>'云相册-城市统计'!B9</f>
         <v>33</v>
       </c>
-      <c r="D60" s="16">
+      <c r="D64" s="16">
         <v>33</v>
       </c>
-      <c r="E60" s="9">
-        <f t="shared" si="3"/>
+      <c r="E64" s="9">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F60" s="53" t="str">
+      <c r="F64" s="53" t="str">
         <f>'云相册-城市统计'!A9</f>
         <v>温州市</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15.6">
-      <c r="A61" s="70"/>
-      <c r="B61" s="39" t="s">
+    <row r="65" spans="1:6" ht="15.6">
+      <c r="A65" s="65"/>
+      <c r="B65" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="C61" s="52">
+      <c r="C65" s="52">
         <f>'云相册-城市统计'!B10</f>
         <v>33</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D65" s="16">
         <v>31</v>
       </c>
-      <c r="E61" s="9">
-        <f t="shared" si="3"/>
+      <c r="E65" s="9">
+        <f t="shared" si="5"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="F61" s="53" t="str">
+      <c r="F65" s="53" t="str">
         <f>'云相册-城市统计'!A10</f>
         <v>六安市</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15.6">
-      <c r="A62" s="71"/>
-      <c r="B62" s="39" t="s">
+    <row r="66" spans="1:6" ht="15.6">
+      <c r="A66" s="66"/>
+      <c r="B66" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="C62" s="52">
+      <c r="C66" s="52">
         <f>'云相册-城市统计'!B11</f>
         <v>32</v>
       </c>
-      <c r="D62" s="16">
+      <c r="D66" s="16">
         <v>31</v>
       </c>
-      <c r="E62" s="9">
-        <f t="shared" si="3"/>
+      <c r="E66" s="9">
+        <f t="shared" si="5"/>
         <v>3.2258064516129031E-2</v>
       </c>
-      <c r="F62" s="53" t="str">
+      <c r="F66" s="53" t="str">
         <f>'云相册-城市统计'!A11</f>
         <v>宁波市</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A53:A62"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="A48:A52"/>
     <mergeCell ref="A2:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A57:A66"/>
+    <mergeCell ref="A37:A42"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="A27:A36"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2746,9 +2837,9 @@
       <c r="A1" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="76"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="75"/>
       <c r="E1" s="18"/>
       <c r="F1" s="19" t="s">
         <v>73</v>
@@ -2758,10 +2849,10 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="78"/>
+      <c r="B2" s="87"/>
       <c r="C2" s="20" t="s">
         <v>76</v>
       </c>
@@ -2775,10 +2866,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="79" t="s">
         <v>77</v>
       </c>
       <c r="C3" s="22" t="s">
@@ -2792,8 +2883,8 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="80"/>
-      <c r="B4" s="83"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="81"/>
       <c r="C4" s="23" t="s">
         <v>37</v>
       </c>
@@ -2805,8 +2896,8 @@
       <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="80"/>
-      <c r="B5" s="82" t="s">
+      <c r="A5" s="89"/>
+      <c r="B5" s="79" t="s">
         <v>79</v>
       </c>
       <c r="C5" s="23" t="s">
@@ -2820,8 +2911,8 @@
       <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="80"/>
-      <c r="B6" s="83"/>
+      <c r="A6" s="89"/>
+      <c r="B6" s="81"/>
       <c r="C6" s="24" t="s">
         <v>81</v>
       </c>
@@ -2833,8 +2924,8 @@
       <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="80"/>
-      <c r="B7" s="84" t="s">
+      <c r="A7" s="89"/>
+      <c r="B7" s="91" t="s">
         <v>82</v>
       </c>
       <c r="C7" s="25" t="s">
@@ -2848,8 +2939,8 @@
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="80"/>
-      <c r="B8" s="85"/>
+      <c r="A8" s="89"/>
+      <c r="B8" s="92"/>
       <c r="C8" s="25" t="s">
         <v>84</v>
       </c>
@@ -2861,8 +2952,8 @@
       <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="80"/>
-      <c r="B9" s="85"/>
+      <c r="A9" s="89"/>
+      <c r="B9" s="92"/>
       <c r="C9" s="25" t="s">
         <v>85</v>
       </c>
@@ -2874,8 +2965,8 @@
       <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="80"/>
-      <c r="B10" s="86"/>
+      <c r="A10" s="89"/>
+      <c r="B10" s="93"/>
       <c r="C10" s="25" t="s">
         <v>86</v>
       </c>
@@ -2887,8 +2978,8 @@
       <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="80"/>
-      <c r="B11" s="84" t="s">
+      <c r="A11" s="89"/>
+      <c r="B11" s="91" t="s">
         <v>87</v>
       </c>
       <c r="C11" s="25" t="s">
@@ -2902,8 +2993,8 @@
       <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="80"/>
-      <c r="B12" s="85"/>
+      <c r="A12" s="89"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="25" t="s">
         <v>89</v>
       </c>
@@ -2915,8 +3006,8 @@
       <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="80"/>
-      <c r="B13" s="85"/>
+      <c r="A13" s="89"/>
+      <c r="B13" s="92"/>
       <c r="C13" s="25" t="s">
         <v>90</v>
       </c>
@@ -2928,8 +3019,8 @@
       <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="80"/>
-      <c r="B14" s="86"/>
+      <c r="A14" s="89"/>
+      <c r="B14" s="93"/>
       <c r="C14" s="25" t="s">
         <v>91</v>
       </c>
@@ -2941,8 +3032,8 @@
       <c r="G14" s="18"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="80"/>
-      <c r="B15" s="82" t="s">
+      <c r="A15" s="89"/>
+      <c r="B15" s="79" t="s">
         <v>92</v>
       </c>
       <c r="C15" s="23" t="s">
@@ -2956,8 +3047,8 @@
       <c r="G15" s="18"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="80"/>
-      <c r="B16" s="87"/>
+      <c r="A16" s="89"/>
+      <c r="B16" s="80"/>
       <c r="C16" s="23" t="s">
         <v>95</v>
       </c>
@@ -2969,8 +3060,8 @@
       <c r="G16" s="18"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="80"/>
-      <c r="B17" s="87"/>
+      <c r="A17" s="89"/>
+      <c r="B17" s="80"/>
       <c r="C17" s="23" t="s">
         <v>96</v>
       </c>
@@ -2982,8 +3073,8 @@
       <c r="G17" s="18"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="80"/>
-      <c r="B18" s="87"/>
+      <c r="A18" s="89"/>
+      <c r="B18" s="80"/>
       <c r="C18" s="23" t="s">
         <v>97</v>
       </c>
@@ -2995,8 +3086,8 @@
       <c r="G18" s="18"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="81"/>
-      <c r="B19" s="83"/>
+      <c r="A19" s="90"/>
+      <c r="B19" s="81"/>
       <c r="C19" s="28" t="s">
         <v>98</v>
       </c>
@@ -3008,10 +3099,10 @@
       <c r="G19" s="18"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="79" t="s">
         <v>100</v>
       </c>
       <c r="C20" s="20" t="s">
@@ -3025,8 +3116,8 @@
       <c r="G20" s="18"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="89"/>
-      <c r="B21" s="87"/>
+      <c r="A21" s="77"/>
+      <c r="B21" s="80"/>
       <c r="C21" s="20" t="s">
         <v>32</v>
       </c>
@@ -3038,8 +3129,8 @@
       <c r="G21" s="18"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="89"/>
-      <c r="B22" s="87"/>
+      <c r="A22" s="77"/>
+      <c r="B22" s="80"/>
       <c r="C22" s="23" t="s">
         <v>102</v>
       </c>
@@ -3051,8 +3142,8 @@
       <c r="G22" s="18"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="89"/>
-      <c r="B23" s="87"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="80"/>
       <c r="C23" s="23" t="s">
         <v>103</v>
       </c>
@@ -3064,8 +3155,8 @@
       <c r="G23" s="18"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="89"/>
-      <c r="B24" s="87"/>
+      <c r="A24" s="77"/>
+      <c r="B24" s="80"/>
       <c r="C24" s="23" t="s">
         <v>104</v>
       </c>
@@ -3077,8 +3168,8 @@
       <c r="G24" s="18"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="89"/>
-      <c r="B25" s="87"/>
+      <c r="A25" s="77"/>
+      <c r="B25" s="80"/>
       <c r="C25" s="23" t="s">
         <v>105</v>
       </c>
@@ -3090,8 +3181,8 @@
       <c r="G25" s="18"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="89"/>
-      <c r="B26" s="87"/>
+      <c r="A26" s="77"/>
+      <c r="B26" s="80"/>
       <c r="C26" s="23" t="s">
         <v>106</v>
       </c>
@@ -3103,8 +3194,8 @@
       <c r="G26" s="18"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="89"/>
-      <c r="B27" s="87"/>
+      <c r="A27" s="77"/>
+      <c r="B27" s="80"/>
       <c r="C27" s="23" t="s">
         <v>107</v>
       </c>
@@ -3116,8 +3207,8 @@
       <c r="G27" s="18"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="89"/>
-      <c r="B28" s="83"/>
+      <c r="A28" s="77"/>
+      <c r="B28" s="81"/>
       <c r="C28" s="23" t="s">
         <v>108</v>
       </c>
@@ -3129,8 +3220,8 @@
       <c r="G28" s="18"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="89"/>
-      <c r="B29" s="91" t="s">
+      <c r="A29" s="77"/>
+      <c r="B29" s="82" t="s">
         <v>109</v>
       </c>
       <c r="C29" s="29" t="s">
@@ -3144,8 +3235,8 @@
       <c r="G29" s="18"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="89"/>
-      <c r="B30" s="92"/>
+      <c r="A30" s="77"/>
+      <c r="B30" s="83"/>
       <c r="C30" s="30" t="s">
         <v>111</v>
       </c>
@@ -3157,8 +3248,8 @@
       <c r="G30" s="18"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="89"/>
-      <c r="B31" s="91" t="s">
+      <c r="A31" s="77"/>
+      <c r="B31" s="82" t="s">
         <v>112</v>
       </c>
       <c r="C31" s="32" t="s">
@@ -3172,8 +3263,8 @@
       <c r="G31" s="18"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="89"/>
-      <c r="B32" s="93"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="84"/>
       <c r="C32" s="32" t="s">
         <v>114</v>
       </c>
@@ -3189,8 +3280,8 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="89"/>
-      <c r="B33" s="93"/>
+      <c r="A33" s="77"/>
+      <c r="B33" s="84"/>
       <c r="C33" s="32" t="s">
         <v>116</v>
       </c>
@@ -3202,8 +3293,8 @@
       <c r="G33" s="17"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="90"/>
-      <c r="B34" s="92"/>
+      <c r="A34" s="78"/>
+      <c r="B34" s="83"/>
       <c r="C34" s="32" t="s">
         <v>117</v>
       </c>
@@ -3219,13 +3310,13 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="88" t="s">
+      <c r="A35" s="76" t="s">
         <v>118</v>
       </c>
       <c r="B35" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="76"/>
+      <c r="C35" s="75"/>
       <c r="D35" s="25">
         <v>321</v>
       </c>
@@ -3236,11 +3327,11 @@
       <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="89"/>
+      <c r="A36" s="77"/>
       <c r="B36" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="76"/>
+      <c r="C36" s="75"/>
       <c r="D36" s="25">
         <v>87707</v>
       </c>
@@ -3251,11 +3342,11 @@
       <c r="G36" s="18"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="89"/>
+      <c r="A37" s="77"/>
       <c r="B37" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="76"/>
+      <c r="C37" s="75"/>
       <c r="D37" s="25">
         <v>63519.1</v>
       </c>
@@ -3266,11 +3357,11 @@
       <c r="G37" s="18"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="89"/>
+      <c r="A38" s="77"/>
       <c r="B38" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="76"/>
+      <c r="C38" s="75"/>
       <c r="D38" s="25">
         <v>36170.99</v>
       </c>
@@ -3281,11 +3372,11 @@
       <c r="G38" s="18"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="89"/>
+      <c r="A39" s="77"/>
       <c r="B39" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="76"/>
+      <c r="C39" s="75"/>
       <c r="D39" s="25">
         <v>27348.11</v>
       </c>
@@ -3296,11 +3387,11 @@
       <c r="G39" s="18"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="90"/>
+      <c r="A40" s="78"/>
       <c r="B40" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="76"/>
+      <c r="C40" s="75"/>
       <c r="D40" s="25">
         <v>11156</v>
       </c>
@@ -3312,6 +3403,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:A19"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="B15:B19"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="A20:A34"/>
     <mergeCell ref="B20:B28"/>
@@ -3323,14 +3422,6 @@
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:A19"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="B15:B19"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
